--- a/data/serie_modelo.xlsx
+++ b/data/serie_modelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30514"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\para cargar simulador electoral arg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D285771B-21B7-4684-8F47-4FFE096BA457}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E009392-1A87-4690-8742-C30C43F6C59E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="245">
   <si>
     <t>YearMonth</t>
   </si>
@@ -765,13 +765,16 @@
   </si>
   <si>
     <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -781,6 +784,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -803,14 +813,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1112,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="9" width="11.5703125" customWidth="1"/>
@@ -1196,7 +1209,7 @@
         <v>143.82451041095939</v>
       </c>
       <c r="I3">
-        <v>98.480761751828467</v>
+        <v>98.480761751828481</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1225,7 +1238,7 @@
         <v>145.11893100465801</v>
       </c>
       <c r="I4">
-        <v>97.602340685657566</v>
+        <v>97.60234068565758</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1283,7 +1296,7 @@
         <v>147.1571263906184</v>
       </c>
       <c r="I6">
-        <v>96.863562904445885</v>
+        <v>96.863562904445899</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1399,7 +1412,7 @@
         <v>151.77105313681079</v>
       </c>
       <c r="I10">
-        <v>90.352316432128973</v>
+        <v>90.352316432128958</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1428,7 +1441,7 @@
         <v>152.37813734935801</v>
       </c>
       <c r="I11">
-        <v>89.400292129190319</v>
+        <v>89.400292129190291</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1457,7 +1470,7 @@
         <v>153.14002803610481</v>
       </c>
       <c r="I12">
-        <v>89.250069240369896</v>
+        <v>89.250069240369882</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1486,7 +1499,7 @@
         <v>153.90572817628529</v>
       </c>
       <c r="I13">
-        <v>90.271485234007955</v>
+        <v>90.27148523400794</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1515,7 +1528,7 @@
         <v>154.5213510889904</v>
       </c>
       <c r="I14">
-        <v>94.290661155975343</v>
+        <v>94.290661155975329</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1573,7 +1586,7 @@
         <v>155.44986988768409</v>
       </c>
       <c r="I16">
-        <v>99.531010346135204</v>
+        <v>99.531010346135176</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1602,7 +1615,7 @@
         <v>156.22711923712251</v>
       </c>
       <c r="I17">
-        <v>99.902033795346242</v>
+        <v>99.902033795346227</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1631,7 +1644,7 @@
         <v>156.852027714071</v>
       </c>
       <c r="I18">
-        <v>100.9419370557266</v>
+        <v>100.94193705572658</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1660,7 +1673,7 @@
         <v>157.79313988035551</v>
       </c>
       <c r="I19">
-        <v>104.3420588303235</v>
+        <v>104.34205883032348</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1689,7 +1702,7 @@
         <v>158.2665192999965</v>
       </c>
       <c r="I20">
-        <v>105.17002337750959</v>
+        <v>105.17002337750958</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1718,7 +1731,7 @@
         <v>158.74131885789649</v>
       </c>
       <c r="I21">
-        <v>105.9921015268857</v>
+        <v>105.99210152688568</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,7 +1760,7 @@
         <v>159.37628413332811</v>
       </c>
       <c r="I22">
-        <v>106.70193829410481</v>
+        <v>106.70193829410482</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1776,7 +1789,7 @@
         <v>160.33254183812801</v>
       </c>
       <c r="I23">
-        <v>107.1909088968944</v>
+        <v>107.19090889689431</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1805,7 +1818,7 @@
         <v>161.61520217283299</v>
       </c>
       <c r="I24">
-        <v>107.1775117079309</v>
+        <v>107.17751170793082</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1834,7 +1847,7 @@
         <v>162.74650858804279</v>
       </c>
       <c r="I25">
-        <v>106.43248431770689</v>
+        <v>106.43248431770687</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1863,7 +1876,7 @@
         <v>164.04848065674719</v>
       </c>
       <c r="I26">
-        <v>105.31281387876609</v>
+        <v>105.31281387876608</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1921,7 +1934,7 @@
         <v>166.84911631851921</v>
       </c>
       <c r="I28">
-        <v>103.0043866253952</v>
+        <v>103.00438662539516</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1950,7 +1963,7 @@
         <v>168.5176074817044</v>
       </c>
       <c r="I29">
-        <v>101.71686525207291</v>
+        <v>101.71686525207284</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1979,7 +1992,7 @@
         <v>170.53981877148479</v>
       </c>
       <c r="I30">
-        <v>101.8332461047641</v>
+        <v>101.83324610476403</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -2037,7 +2050,7 @@
         <v>173.79508283219491</v>
       </c>
       <c r="I32">
-        <v>100.7045043397306</v>
+        <v>100.70450433973059</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2066,7 +2079,7 @@
         <v>175.01164841202029</v>
       </c>
       <c r="I33">
-        <v>100.5199600029048</v>
+        <v>100.51996000290477</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2124,7 +2137,7 @@
         <v>177.6466237905116</v>
       </c>
       <c r="I35">
-        <v>99.790741066961445</v>
+        <v>99.790741066961417</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2153,7 +2166,7 @@
         <v>178.89015015704521</v>
       </c>
       <c r="I36">
-        <v>99.349217008631214</v>
+        <v>99.3492170086312</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2182,7 +2195,7 @@
         <v>180.14238120814451</v>
       </c>
       <c r="I37">
-        <v>98.909009316533854</v>
+        <v>98.909009316533826</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2211,7 +2224,7 @@
         <v>181.5835202578096</v>
       </c>
       <c r="I38">
-        <v>98.372432412465855</v>
+        <v>98.372432412465827</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2240,7 +2253,7 @@
         <v>182.85460489961429</v>
       </c>
       <c r="I39">
-        <v>97.93530054203643</v>
+        <v>97.935300542036401</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2269,7 +2282,7 @@
         <v>184.3174417388112</v>
       </c>
       <c r="I40">
-        <v>97.402766821924587</v>
+        <v>97.402766821924573</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2298,7 +2311,7 @@
         <v>185.6076638309828</v>
       </c>
       <c r="I41">
-        <v>100.3711274781426</v>
+        <v>100.37112747814257</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2356,7 +2369,7 @@
         <v>188.4021728176221</v>
       </c>
       <c r="I43">
-        <v>99.361203920621449</v>
+        <v>99.361203920621421</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2385,7 +2398,7 @@
         <v>189.9093902001631</v>
       </c>
       <c r="I44">
-        <v>102.1354888264181</v>
+        <v>102.13548882641805</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2443,7 +2456,7 @@
         <v>192.5774272230851</v>
       </c>
       <c r="I46">
-        <v>100.0177660532769</v>
+        <v>100.01776605327686</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2472,7 +2485,7 @@
         <v>194.11804664086981</v>
       </c>
       <c r="I47">
-        <v>100.85059678804269</v>
+        <v>100.85059678804265</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2501,7 +2514,7 @@
         <v>195.6709910139968</v>
       </c>
       <c r="I48">
-        <v>102.1249688599565</v>
+        <v>102.12496885995648</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2530,7 +2543,7 @@
         <v>197.23635894210869</v>
       </c>
       <c r="I49">
-        <v>101.3144532340839</v>
+        <v>101.31445323408381</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2588,7 +2601,7 @@
         <v>199.61029575833601</v>
       </c>
       <c r="I51">
-        <v>104.403171808195</v>
+        <v>104.40317180819495</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2617,7 +2630,7 @@
         <v>201.20717812440259</v>
       </c>
       <c r="I52">
-        <v>106.04063652098419</v>
+        <v>106.04063652098412</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2646,7 +2659,7 @@
         <v>203.01804272752219</v>
       </c>
       <c r="I53">
-        <v>106.20572198423579</v>
+        <v>106.20572198423577</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2675,7 +2688,7 @@
         <v>204.43916902661491</v>
       </c>
       <c r="I54">
-        <v>103.922947431941</v>
+        <v>103.92294743194095</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2704,7 +2717,7 @@
         <v>206.2791215478544</v>
       </c>
       <c r="I55">
-        <v>107.5881611915583</v>
+        <v>107.58816119155823</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2762,7 +2775,7 @@
         <v>209.59278935639909</v>
       </c>
       <c r="I57">
-        <v>126.9785401117653</v>
+        <v>126.97854011176528</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2820,7 +2833,7 @@
         <v>212.74841839294911</v>
       </c>
       <c r="I59">
-        <v>133.36410683845779</v>
+        <v>133.36410683845773</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2849,7 +2862,7 @@
         <v>214.66315415848561</v>
       </c>
       <c r="I60">
-        <v>133.43534239920319</v>
+        <v>133.43534239920317</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2878,7 +2891,7 @@
         <v>216.59512254591189</v>
       </c>
       <c r="I61">
-        <v>130.78731577487591</v>
+        <v>130.78731577487585</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2907,7 +2920,7 @@
         <v>218.32788352627921</v>
       </c>
       <c r="I62">
-        <v>130.57575000271959</v>
+        <v>130.57575000271956</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2936,7 +2949,7 @@
         <v>220.29283447801569</v>
       </c>
       <c r="I63">
-        <v>131.4586937526596</v>
+        <v>131.45869375265954</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2965,7 +2978,7 @@
         <v>222.49576282279591</v>
       </c>
       <c r="I64">
-        <v>137.4556527625663</v>
+        <v>137.45565276256622</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2994,7 +3007,7 @@
         <v>224.9432162138466</v>
       </c>
       <c r="I65">
-        <v>158.21904482793229</v>
+        <v>158.21904482793218</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3081,7 +3094,7 @@
         <v>229.2439606757271</v>
       </c>
       <c r="I68">
-        <v>184.37258431663551</v>
+        <v>184.37258431663545</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -3110,7 +3123,7 @@
         <v>230.84866840045709</v>
       </c>
       <c r="I69">
-        <v>170.9760717422611</v>
+        <v>170.97607174226098</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -3139,7 +3152,7 @@
         <v>232.69545774766081</v>
       </c>
       <c r="I70">
-        <v>155.08033718118921</v>
+        <v>155.08033718118912</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -3168,7 +3181,7 @@
         <v>234.7897168673897</v>
       </c>
       <c r="I71">
-        <v>162.91888742523349</v>
+        <v>162.91888742523338</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -3197,7 +3210,7 @@
         <v>236.66803460232879</v>
       </c>
       <c r="I72">
-        <v>175.34883249009661</v>
+        <v>175.34883249009653</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -3226,7 +3239,7 @@
         <v>238.56137887914741</v>
       </c>
       <c r="I73">
-        <v>178.30610446661609</v>
+        <v>178.30610446661603</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3284,7 +3297,7 @@
         <v>242.8748071706612</v>
       </c>
       <c r="I75">
-        <v>176.99666659753331</v>
+        <v>176.99666659753325</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3313,7 +3326,7 @@
         <v>246.27505447105051</v>
       </c>
       <c r="I76">
-        <v>182.24570934984271</v>
+        <v>182.2457093498426</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -3342,7 +3355,7 @@
         <v>255.14095643200841</v>
       </c>
       <c r="I77">
-        <v>197.12846658492711</v>
+        <v>197.12846658492705</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3371,7 +3384,7 @@
         <v>263.81574895069662</v>
       </c>
       <c r="I78">
-        <v>191.50140303676639</v>
+        <v>191.50140303676633</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -3400,7 +3413,7 @@
         <v>270.67495842341481</v>
       </c>
       <c r="I79">
-        <v>178.3160168209935</v>
+        <v>178.31601682099344</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3429,7 +3442,7 @@
         <v>275.54710767503627</v>
       </c>
       <c r="I80">
-        <v>171.07048599777659</v>
+        <v>171.07048599777656</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -3458,7 +3471,7 @@
         <v>279.40476718248681</v>
       </c>
       <c r="I81">
-        <v>182.43127240403501</v>
+        <v>182.43127240403496</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -3487,7 +3500,7 @@
         <v>283.03702915585899</v>
       </c>
       <c r="I82">
-        <v>192.0429839055659</v>
+        <v>192.04298390556582</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -3574,7 +3587,7 @@
         <v>294.80076926592687</v>
       </c>
       <c r="I85">
-        <v>238.6990229669257</v>
+        <v>238.69902296692572</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3632,7 +3645,7 @@
         <v>301.62010066058622</v>
       </c>
       <c r="I87">
-        <v>194.41856228955609</v>
+        <v>194.41856228955612</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -3719,7 +3732,7 @@
         <v>310.75918669440102</v>
       </c>
       <c r="I90">
-        <v>187.6848442054212</v>
+        <v>187.68484420542117</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3777,7 +3790,7 @@
         <v>318.26184573876378</v>
       </c>
       <c r="I92">
-        <v>178.58320934992889</v>
+        <v>178.58320934992898</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3806,7 +3819,7 @@
         <v>321.44446419615139</v>
       </c>
       <c r="I93">
-        <v>176.11341170372529</v>
+        <v>176.11341170372535</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3864,7 +3877,7 @@
         <v>328.8794746530084</v>
       </c>
       <c r="I95">
-        <v>202.85516007558701</v>
+        <v>202.85516007558698</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3922,7 +3935,7 @@
         <v>336.81994068903049</v>
       </c>
       <c r="I97">
-        <v>212.1348580162701</v>
+        <v>212.13485801627004</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3951,7 +3964,7 @@
         <v>340.52496003660991</v>
       </c>
       <c r="I98">
-        <v>206.64757022836011</v>
+        <v>206.64757022836005</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -3980,7 +3993,7 @@
         <v>347.33545923734209</v>
       </c>
       <c r="I99">
-        <v>189.47888698037789</v>
+        <v>189.47888698037792</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -4009,7 +4022,7 @@
         <v>360.8815421475984</v>
       </c>
       <c r="I100">
-        <v>177.1168320696375</v>
+        <v>177.11683206963747</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -4038,7 +4051,7 @@
         <v>375.6776853756499</v>
       </c>
       <c r="I101">
-        <v>166.5389096992179</v>
+        <v>166.53890969921784</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -4067,7 +4080,7 @@
         <v>385.82098288079243</v>
       </c>
       <c r="I102">
-        <v>177.82713291420791</v>
+        <v>177.82713291420779</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -4096,7 +4109,7 @@
         <v>397.39561236721619</v>
       </c>
       <c r="I103">
-        <v>168.67487505697761</v>
+        <v>168.67487505697758</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -4125,7 +4138,7 @@
         <v>410.90706318770162</v>
       </c>
       <c r="I104">
-        <v>156.5418905472678</v>
+        <v>156.54189054726777</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -4154,7 +4167,7 @@
         <v>428.16515984158508</v>
       </c>
       <c r="I105">
-        <v>148.65185865607651</v>
+        <v>148.65185865607646</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -4212,7 +4225,7 @@
         <v>450.26704539260771</v>
       </c>
       <c r="I107">
-        <v>150.97246472639219</v>
+        <v>150.97246472639222</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -4241,7 +4254,7 @@
         <v>451.1675794833929</v>
       </c>
       <c r="I108">
-        <v>150.07123745496051</v>
+        <v>150.07123745496048</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -4270,7 +4283,7 @@
         <v>456.13042285771019</v>
       </c>
       <c r="I109">
-        <v>151.40520532868919</v>
+        <v>151.40520532868925</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -4299,7 +4312,7 @@
         <v>467.07755300629532</v>
       </c>
       <c r="I110">
-        <v>146.4080176854722</v>
+        <v>146.40801768547217</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -4386,7 +4399,7 @@
         <v>486.48859362459717</v>
       </c>
       <c r="I113">
-        <v>150.5802515362696</v>
+        <v>150.58025153626966</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -4415,7 +4428,7 @@
         <v>498.65080846521198</v>
       </c>
       <c r="I114">
-        <v>143.65099089246439</v>
+        <v>143.65099089246442</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -4444,7 +4457,7 @@
         <v>510.61842786837718</v>
       </c>
       <c r="I115">
-        <v>137.63396605551131</v>
+        <v>137.63396605551128</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -4502,7 +4515,7 @@
         <v>530.70513558386324</v>
       </c>
       <c r="I117">
-        <v>135.9095044448066</v>
+        <v>135.90950444480652</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -4531,7 +4544,7 @@
         <v>537.07359721086971</v>
       </c>
       <c r="I118">
-        <v>138.077420736813</v>
+        <v>138.07742073681297</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -4618,7 +4631,7 @@
         <v>564.373865583113</v>
       </c>
       <c r="I121">
-        <v>139.9503235519901</v>
+        <v>139.95032355199007</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -4647,7 +4660,7 @@
         <v>572.83947356685962</v>
       </c>
       <c r="I122">
-        <v>139.37824279835729</v>
+        <v>139.37824279835723</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -4705,7 +4718,7 @@
         <v>598.86586220889637</v>
       </c>
       <c r="I124">
-        <v>142.20900186102719</v>
+        <v>142.20900186102716</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -4763,7 +4776,7 @@
         <v>624.27693847414434</v>
       </c>
       <c r="I126">
-        <v>144.1518643588704</v>
+        <v>144.15186435887037</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -4792,7 +4805,7 @@
         <v>638.63530805904952</v>
       </c>
       <c r="I127">
-        <v>143.80682685925959</v>
+        <v>143.80682685925964</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -4821,7 +4834,7 @@
         <v>655.87846137664383</v>
       </c>
       <c r="I128">
-        <v>141.67672418859499</v>
+        <v>141.67672418859502</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -4879,7 +4892,7 @@
         <v>694.42902970097862</v>
       </c>
       <c r="I130">
-        <v>184.47823203142761</v>
+        <v>184.47823203142755</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -4908,7 +4921,7 @@
         <v>715.95632962170896</v>
       </c>
       <c r="I131">
-        <v>172.945979879465</v>
+        <v>172.94597987946497</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -4966,7 +4979,7 @@
         <v>792.23073719795764</v>
       </c>
       <c r="I133">
-        <v>223.76673112683361</v>
+        <v>223.76673112683358</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -4995,7 +5008,7 @@
         <v>835.01119700664731</v>
       </c>
       <c r="I134">
-        <v>186.37233714954201</v>
+        <v>186.37233714954198</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -5053,7 +5066,7 @@
         <v>884.13657574894251</v>
       </c>
       <c r="I136">
-        <v>196.42466799778529</v>
+        <v>196.42466799778521</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -5082,7 +5095,7 @@
         <v>909.77653644566169</v>
       </c>
       <c r="I137">
-        <v>176.0144312072338</v>
+        <v>176.01443120723374</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -5111,7 +5124,7 @@
         <v>944.3480448305969</v>
       </c>
       <c r="I138">
-        <v>185.33365710984481</v>
+        <v>185.33365710984472</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -5169,7 +5182,7 @@
         <v>1022.349304637515</v>
       </c>
       <c r="I140">
-        <v>198.5490728065659</v>
+        <v>198.54907280656587</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -5198,7 +5211,7 @@
         <v>1054.0421330812769</v>
       </c>
       <c r="I141">
-        <v>190.4393520830302</v>
+        <v>190.43935208303014</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -5227,7 +5240,7 @@
         <v>1082.5012706744719</v>
       </c>
       <c r="I142">
-        <v>176.26521215085219</v>
+        <v>176.26521215085228</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -5256,7 +5269,7 @@
         <v>1106.31629862931</v>
       </c>
       <c r="I143">
-        <v>178.17910857106409</v>
+        <v>178.17910857106415</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -5285,7 +5298,7 @@
         <v>1150.5689505744831</v>
       </c>
       <c r="I144">
-        <v>235.23029647649719</v>
+        <v>235.23029647649727</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -5314,7 +5327,7 @@
         <v>1218.4525186583769</v>
       </c>
       <c r="I145">
-        <v>215.64628218061009</v>
+        <v>215.64628218061011</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -5372,7 +5385,7 @@
         <v>1312.78389420039</v>
       </c>
       <c r="I147">
-        <v>227.63932969511379</v>
+        <v>227.63932969511382</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -5401,7 +5414,7 @@
         <v>1361.3568982858039</v>
       </c>
       <c r="I148">
-        <v>243.5398298079127</v>
+        <v>243.53982980791272</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -5459,7 +5472,7 @@
         <v>1420.5214690853049</v>
       </c>
       <c r="I150">
-        <v>236.57188285140711</v>
+        <v>236.57188285140708</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -5488,7 +5501,7 @@
         <v>1467.3986775651199</v>
       </c>
       <c r="I151">
-        <v>241.31048297245209</v>
+        <v>241.31048297245218</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -5517,7 +5530,7 @@
         <v>1489.409657728597</v>
       </c>
       <c r="I152">
-        <v>327.08772440180508</v>
+        <v>327.08772440180525</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5546,7 +5559,7 @@
         <v>1511.750802594526</v>
       </c>
       <c r="I153">
-        <v>343.14074353409592</v>
+        <v>343.14074353409603</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -5575,7 +5588,7 @@
         <v>1545.009320251605</v>
       </c>
       <c r="I154">
-        <v>338.67375350936038</v>
+        <v>338.67375350936049</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -5604,7 +5617,7 @@
         <v>1574.3644973363851</v>
       </c>
       <c r="I155">
-        <v>375.3363820998124</v>
+        <v>375.33638209981245</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -5633,7 +5646,7 @@
         <v>1616.872338764467</v>
       </c>
       <c r="I156">
-        <v>365.46872648472493</v>
+        <v>365.46872648472487</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -5662,7 +5675,7 @@
         <v>1662.1447642498731</v>
       </c>
       <c r="I157">
-        <v>379.93897368240022</v>
+        <v>379.93897368240027</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -5691,7 +5704,7 @@
         <v>1725.3062652913679</v>
       </c>
       <c r="I158">
-        <v>426.16331344777888</v>
+        <v>426.16331344777905</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -5720,7 +5733,7 @@
         <v>1780.5160657806921</v>
       </c>
       <c r="I159">
-        <v>377.48093940956301</v>
+        <v>377.48093940956318</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -5749,7 +5762,7 @@
         <v>1851.7367084119189</v>
       </c>
       <c r="I160">
-        <v>389.75832670063312</v>
+        <v>389.75832670063306</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -5778,7 +5791,7 @@
         <v>1925.806176748396</v>
       </c>
       <c r="I161">
-        <v>346.66005019046679</v>
+        <v>346.6600501904669</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -5807,7 +5820,7 @@
         <v>1995.135199111339</v>
       </c>
       <c r="I162">
-        <v>318.78761267906589</v>
+        <v>318.787612679066</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
@@ -5836,7 +5849,7 @@
         <v>2090.9016886686832</v>
       </c>
       <c r="I163">
-        <v>293.39989256370097</v>
+        <v>293.39989256370103</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -5865,7 +5878,7 @@
         <v>2176.6286579040989</v>
       </c>
       <c r="I164">
-        <v>300.49573671905301</v>
+        <v>300.49573671905307</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -5894,7 +5907,7 @@
         <v>2248.4574036149338</v>
       </c>
       <c r="I165">
-        <v>304.93942638646092</v>
+        <v>304.93942638646104</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -5923,7 +5936,7 @@
         <v>2320.4080405306122</v>
       </c>
       <c r="I166">
-        <v>316.86764650265923</v>
+        <v>316.86764650265928</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -5952,7 +5965,7 @@
         <v>2390.0202817465311</v>
       </c>
       <c r="I167">
-        <v>331.23040062670009</v>
+        <v>331.23040062670026</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -5981,7 +5994,7 @@
         <v>2449.7707887901938</v>
       </c>
       <c r="I168">
-        <v>324.99293008470607</v>
+        <v>324.9929300847063</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -6010,7 +6023,7 @@
         <v>2535.512766397851</v>
       </c>
       <c r="I169">
-        <v>323.78762176741259</v>
+        <v>323.78762176741282</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -6039,7 +6052,7 @@
         <v>2624.2557132217748</v>
       </c>
       <c r="I170">
-        <v>332.60553597703642</v>
+        <v>332.6055359770366</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -6068,7 +6081,7 @@
         <v>2689.8621060523192</v>
       </c>
       <c r="I171">
-        <v>331.20107571923973</v>
+        <v>331.20107571923978</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -6097,7 +6110,7 @@
         <v>2792.0768660823069</v>
       </c>
       <c r="I172">
-        <v>329.57742224201797</v>
+        <v>329.57742224201809</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -6126,7 +6139,7 @@
         <v>2900.9678638595169</v>
       </c>
       <c r="I173">
-        <v>324.98103969022702</v>
+        <v>324.98103969022713</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -6155,7 +6168,7 @@
         <v>3037.3133534609151</v>
       </c>
       <c r="I174">
-        <v>307.4223240512971</v>
+        <v>307.42232405129727</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -6184,7 +6197,7 @@
         <v>3240.8133481427958</v>
       </c>
       <c r="I175">
-        <v>272.80775262284089</v>
+        <v>272.80775262284101</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -6213,7 +6226,7 @@
         <v>3435.2621490313641</v>
       </c>
       <c r="I176">
-        <v>258.02234978045931</v>
+        <v>258.02234978045942</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -6242,7 +6255,7 @@
         <v>3610.4605186319632</v>
       </c>
       <c r="I177">
-        <v>251.123937729836</v>
+        <v>251.12393772983611</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -6271,7 +6284,7 @@
         <v>3801.8149261194571</v>
       </c>
       <c r="I178">
-        <v>277.63840545034378</v>
+        <v>277.63840545034395</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -6300,7 +6313,7 @@
         <v>4083.1492306522969</v>
       </c>
       <c r="I179">
-        <v>315.95514793645577</v>
+        <v>315.95514793645594</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -6329,7 +6342,7 @@
         <v>4368.9696767979594</v>
       </c>
       <c r="I180">
-        <v>294.25271930556789</v>
+        <v>294.25271930556806</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -6358,7 +6371,7 @@
         <v>4639.8457967594322</v>
       </c>
       <c r="I181">
-        <v>276.10193373238599</v>
+        <v>276.10193373238616</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -6387,7 +6400,7 @@
         <v>4932.156081955276</v>
       </c>
       <c r="I182">
-        <v>261.5675574293536</v>
+        <v>261.56755742935377</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -6416,7 +6429,7 @@
         <v>5173.8317299710834</v>
       </c>
       <c r="I183">
-        <v>270.27386323004811</v>
+        <v>270.27386323004816</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -6445,7 +6458,7 @@
         <v>5437.6971481996088</v>
       </c>
       <c r="I184">
-        <v>283.70418717865152</v>
+        <v>283.70418717865158</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -6474,7 +6487,7 @@
         <v>5763.9589770915854</v>
       </c>
       <c r="I185">
-        <v>296.60125493961408</v>
+        <v>296.60125493961425</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -6503,7 +6516,7 @@
         <v>6144.3802695796303</v>
       </c>
       <c r="I186">
-        <v>273.83275849964622</v>
+        <v>273.83275849964627</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -6532,7 +6545,7 @@
         <v>6617.4975503372634</v>
       </c>
       <c r="I187">
-        <v>264.47985118493358</v>
+        <v>264.47985118493375</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -6561,7 +6574,7 @@
         <v>7173.3673445655922</v>
       </c>
       <c r="I188">
-        <v>290.51834378076461</v>
+        <v>290.51834378076472</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -6590,7 +6603,7 @@
         <v>7732.88999744171</v>
       </c>
       <c r="I189">
-        <v>282.91407997347739</v>
+        <v>282.91407997347756</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -6619,7 +6632,7 @@
         <v>8196.8633972882126</v>
       </c>
       <c r="I190">
-        <v>269.10131318231947</v>
+        <v>269.10131318231959</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -6648,7 +6661,7 @@
         <v>8713.2657913173698</v>
       </c>
       <c r="I191">
-        <v>282.14359499653551</v>
+        <v>282.14359499653563</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -6677,7 +6690,7 @@
         <v>9793.7107494407246</v>
       </c>
       <c r="I192">
-        <v>333.92227361730409</v>
+        <v>333.92227361730437</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -6706,7 +6719,7 @@
         <v>11037.5120146197</v>
       </c>
       <c r="I193">
-        <v>322.85726054238631</v>
+        <v>322.85726054238648</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -6735,7 +6748,7 @@
         <v>11953.62551183313</v>
       </c>
       <c r="I194">
-        <v>328.30255463828342</v>
+        <v>328.30255463828354</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -6764,7 +6777,7 @@
         <v>13483.68957734777</v>
       </c>
       <c r="I195">
-        <v>286.03028879894458</v>
+        <v>286.03028879894475</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -6793,7 +6806,7 @@
         <v>16922.030419571449</v>
       </c>
       <c r="I196">
-        <v>259.9003113431383</v>
+        <v>259.90031134313847</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -6822,7 +6835,7 @@
         <v>20407.96868600318</v>
       </c>
       <c r="I197">
-        <v>253.08147849461531</v>
+        <v>253.08147849461542</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -6851,7 +6864,7 @@
         <v>23101.8205525556</v>
       </c>
       <c r="I198">
-        <v>195.25782592514329</v>
+        <v>195.25782592514341</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -6880,7 +6893,7 @@
         <v>25643.02081333672</v>
       </c>
       <c r="I199">
-        <v>172.38979225823459</v>
+        <v>172.38979225823471</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -6909,7 +6922,7 @@
         <v>27899.606644910349</v>
       </c>
       <c r="I200">
-        <v>163.29690330583821</v>
+        <v>163.2969033058383</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -6938,7 +6951,7 @@
         <v>29071.390123996589</v>
       </c>
       <c r="I201">
-        <v>185.42007891381451</v>
+        <v>185.42007891381462</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -6967,7 +6980,7 @@
         <v>30408.674069700432</v>
       </c>
       <c r="I202">
-        <v>198.0333970814838</v>
+        <v>198.03339708148394</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -6996,7 +7009,7 @@
         <v>31625.02103248845</v>
       </c>
       <c r="I203">
-        <v>191.12989922874411</v>
+        <v>191.12989922874425</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -7025,7 +7038,7 @@
         <v>32953.271915852973</v>
       </c>
       <c r="I204">
-        <v>174.5284767501137</v>
+        <v>174.52847675011378</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -7054,7 +7067,7 @@
         <v>34106.636432907821</v>
       </c>
       <c r="I205">
-        <v>159.3686194819642</v>
+        <v>159.36861948196429</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -7083,7 +7096,7 @@
         <v>35027.515616596327</v>
       </c>
       <c r="I206">
-        <v>148.09594266364891</v>
+        <v>148.09594266364908</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -7112,7 +7125,7 @@
         <v>35868.175991394652</v>
       </c>
       <c r="I207">
-        <v>137.07929475490599</v>
+        <v>137.07929475490616</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -7141,7 +7154,7 @@
         <v>36836.616743162303</v>
       </c>
       <c r="I208">
-        <v>146.33318495315709</v>
+        <v>146.33318495315729</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
@@ -7170,7 +7183,7 @@
         <v>37647.022311511857</v>
       </c>
       <c r="I209">
-        <v>143.7822482324334</v>
+        <v>143.78224823243352</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -7199,7 +7212,7 @@
         <v>38550.550846988153</v>
       </c>
       <c r="I210">
-        <v>141.58245472106481</v>
+        <v>141.58245472106489</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -7228,7 +7241,7 @@
         <v>39976.921228326697</v>
       </c>
       <c r="I211">
-        <v>144.42929145816601</v>
+        <v>144.42929145816612</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7257,7 +7270,7 @@
         <v>41096.275022719863</v>
       </c>
       <c r="I212">
-        <v>129.5192150418257</v>
+        <v>129.51921504182579</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -7286,7 +7299,7 @@
         <v>41712.719148060649</v>
       </c>
       <c r="I213">
-        <v>125.44233902356</v>
+        <v>125.44233902356008</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -7315,7 +7328,7 @@
         <v>42380.122654429622</v>
       </c>
       <c r="I214">
-        <v>126.65997780175501</v>
+        <v>126.6599778017551</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -7344,7 +7357,7 @@
         <v>43185.344984863783</v>
       </c>
       <c r="I215">
-        <v>135.78806965329451</v>
+        <v>135.78806965329463</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -7373,7 +7386,7 @@
         <v>44005.866539576193</v>
       </c>
       <c r="I216">
-        <v>133.25620181873859</v>
+        <v>133.25620181873862</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -7402,7 +7415,7 @@
         <v>44929.989736907279</v>
       </c>
       <c r="I217">
-        <v>143.06493452249109</v>
+        <v>143.06493452249117</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -7431,7 +7444,7 @@
         <v>45963.379500856143</v>
       </c>
       <c r="I218">
-        <v>139.8484208430998</v>
+        <v>139.84842084309992</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -7460,7 +7473,7 @@
         <v>47112.463988377538</v>
       </c>
       <c r="I219">
-        <v>135.48002772305441</v>
+        <v>135.48002772305443</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -7489,7 +7502,7 @@
         <v>48431.612980052108</v>
       </c>
       <c r="I220">
-        <v>140.63799608269659</v>
+        <v>140.63799608269665</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -7518,7 +7531,7 @@
         <v>49836.129756473623</v>
       </c>
       <c r="I221">
-        <v>131.24366505120389</v>
+        <v>131.24366505120392</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -7547,7 +7560,7 @@
         <v>51281.377519411362</v>
       </c>
       <c r="I222">
-        <v>123.5865751127251</v>
+        <v>123.58657511272513</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -7576,7 +7589,7 @@
         <v>53024.944355071333</v>
       </c>
       <c r="I223">
-        <v>118.2467557883821</v>
+        <v>118.24675578838213</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -7605,7 +7618,7 @@
         <v>54403.592908303202</v>
       </c>
       <c r="I224">
-        <v>115.66481854852471</v>
+        <v>115.66481854852472</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -7634,7 +7647,7 @@
         <v>55546.068359377547</v>
       </c>
       <c r="I225">
-        <v>114.5039434621478</v>
+        <v>114.50394346214784</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -7663,7 +7676,7 @@
         <v>56601.443658205717</v>
       </c>
       <c r="I226">
-        <v>119.1429474564209</v>
+        <v>119.14294745642096</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -7692,7 +7705,7 @@
         <v>57790.073975028041</v>
       </c>
       <c r="I227">
-        <v>120.2048873868744</v>
+        <v>120.20488738687452</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -7718,11 +7731,43 @@
         <v>1590</v>
       </c>
       <c r="H228">
-        <v>58945.875454528599</v>
+        <v>58772.505232603515</v>
       </c>
       <c r="I228">
-        <v>121.67416026555289</v>
-      </c>
+        <v>122.03308109229494</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>244</v>
+      </c>
+      <c r="B229" t="s">
+        <v>240</v>
+      </c>
+      <c r="C229" t="s">
+        <v>242</v>
+      </c>
+      <c r="D229">
+        <v>642</v>
+      </c>
+      <c r="E229">
+        <v>250</v>
+      </c>
+      <c r="F229">
+        <v>1.94</v>
+      </c>
+      <c r="G229">
+        <v>1625</v>
+      </c>
+      <c r="H229">
+        <v>59947.955337255589</v>
+      </c>
+      <c r="I229">
+        <v>122.65009383428335</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H231" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/serie_modelo.xlsx
+++ b/data/serie_modelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\para cargar simulador electoral arg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\excel_simulador_electoral\SEPT26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E009392-1A87-4690-8742-C30C43F6C59E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F346819FD96AA6D9731F737A19CA3255452DE7CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB2E6FD-A757-4CF9-AF7D-C8E0942D7369}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="246">
   <si>
     <t>YearMonth</t>
   </si>
@@ -740,6 +740,12 @@
     <t>2026-07</t>
   </si>
   <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
     <t>Otro</t>
   </si>
   <si>
@@ -764,17 +770,14 @@
     <t>S1</t>
   </si>
   <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>2026-09</t>
+    <t>2026-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -783,17 +786,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -804,7 +801,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -812,18 +809,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1125,11 +1147,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="9" width="11.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1165,22 +1184,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2">
-        <v>334.20333333333332</v>
+        <v>334.2</v>
       </c>
       <c r="E2">
-        <v>227.75399999999999</v>
+        <v>227.75</v>
       </c>
       <c r="F2">
-        <v>1.6777739230006901</v>
+        <v>1.6778</v>
       </c>
       <c r="G2">
         <v>3.16</v>
       </c>
       <c r="H2">
-        <v>142.54163568975159</v>
+        <v>100</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -1191,25 +1210,25 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D3">
-        <v>397.03244999999998</v>
+        <v>397.03</v>
       </c>
       <c r="E3">
-        <v>272.53070000000002</v>
+        <v>272.52999999999997</v>
       </c>
       <c r="F3">
-        <v>1.981124028835928</v>
+        <v>1.9811000000000001</v>
       </c>
       <c r="G3">
         <v>3.14</v>
       </c>
       <c r="H3">
-        <v>143.82451041095939</v>
+        <v>100.9</v>
       </c>
       <c r="I3">
-        <v>98.480761751828481</v>
+        <v>98.480761751828496</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1217,28 +1236,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D4">
-        <v>394.20620000000002</v>
+        <v>394.21</v>
       </c>
       <c r="E4">
-        <v>277.79944999999998</v>
+        <v>277.8</v>
       </c>
       <c r="F4">
-        <v>2.0435542312112189</v>
+        <v>2.0436000000000001</v>
       </c>
       <c r="G4">
         <v>3.14</v>
       </c>
       <c r="H4">
-        <v>145.11893100465801</v>
+        <v>101.8081</v>
       </c>
       <c r="I4">
-        <v>97.60234068565758</v>
+        <v>97.602340685657595</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1246,28 +1265,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D5">
-        <v>443.16371428571432</v>
+        <v>443.16</v>
       </c>
       <c r="E5">
-        <v>306.13823809523808</v>
+        <v>306.14</v>
       </c>
       <c r="F5">
-        <v>2.3688267397151068</v>
+        <v>2.3687999999999998</v>
       </c>
       <c r="G5">
         <v>3.14</v>
       </c>
       <c r="H5">
-        <v>146.42500138369991</v>
+        <v>102.72437290000001</v>
       </c>
       <c r="I5">
-        <v>96.731754891632875</v>
+        <v>96.731754891632903</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1275,25 +1294,25 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D6">
-        <v>476.65705000000003</v>
+        <v>476.66</v>
       </c>
       <c r="E6">
-        <v>319.74164999999999</v>
+        <v>319.74</v>
       </c>
       <c r="F6">
-        <v>1.97699051445354</v>
+        <v>1.9770000000000001</v>
       </c>
       <c r="G6">
         <v>3.16</v>
       </c>
       <c r="H6">
-        <v>147.1571263906184</v>
+        <v>103.2379947645</v>
       </c>
       <c r="I6">
         <v>96.863562904445899</v>
@@ -1304,28 +1323,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D7">
-        <v>528.84960000000001</v>
+        <v>528.85</v>
       </c>
       <c r="E7">
-        <v>344.03050000000002</v>
+        <v>344.03</v>
       </c>
       <c r="F7">
-        <v>1.861109390011157</v>
+        <v>1.8611</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>148.77585478091521</v>
+        <v>104.373612706909</v>
       </c>
       <c r="I7">
-        <v>95.506461564876417</v>
+        <v>95.506461564876403</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1333,28 +1352,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D8">
-        <v>555.56195454545457</v>
+        <v>555.55999999999995</v>
       </c>
       <c r="E8">
-        <v>321.50140909090908</v>
+        <v>321.5</v>
       </c>
       <c r="F8">
-        <v>1.7395130942579671</v>
+        <v>1.7395</v>
       </c>
       <c r="G8">
         <v>3.17</v>
       </c>
       <c r="H8">
-        <v>149.96606161916259</v>
+        <v>105.208601608565</v>
       </c>
       <c r="I8">
-        <v>95.35005138594677</v>
+        <v>95.350051385946799</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1362,25 +1381,25 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D9">
-        <v>552.70480952380944</v>
+        <v>552.70000000000005</v>
       </c>
       <c r="E9">
-        <v>297.95371428571428</v>
+        <v>297.95</v>
       </c>
       <c r="F9">
-        <v>1.3343461651288071</v>
+        <v>1.3343</v>
       </c>
       <c r="G9">
         <v>3.15</v>
       </c>
       <c r="H9">
-        <v>150.86585798887751</v>
+        <v>105.83985321821601</v>
       </c>
       <c r="I9">
         <v>94.183373533478104</v>
@@ -1391,28 +1410,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D10">
-        <v>561.7461428571429</v>
+        <v>561.75</v>
       </c>
       <c r="E10">
-        <v>293.25557142857139</v>
+        <v>293.26</v>
       </c>
       <c r="F10">
-        <v>1.207620822336096</v>
+        <v>1.2076</v>
       </c>
       <c r="G10">
         <v>3.04</v>
       </c>
       <c r="H10">
-        <v>151.77105313681079</v>
+        <v>106.47489233752501</v>
       </c>
       <c r="I10">
-        <v>90.352316432128958</v>
+        <v>90.352316432129001</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1420,28 +1439,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D11">
-        <v>626.6585</v>
+        <v>626.66</v>
       </c>
       <c r="E11">
-        <v>335.18336363636359</v>
+        <v>335.18</v>
       </c>
       <c r="F11">
-        <v>1.268698417376326</v>
+        <v>1.2686999999999999</v>
       </c>
       <c r="G11">
         <v>3.02</v>
       </c>
       <c r="H11">
-        <v>152.37813734935801</v>
+        <v>106.90079190687599</v>
       </c>
       <c r="I11">
-        <v>89.400292129190291</v>
+        <v>89.400292129190305</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1449,28 +1468,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D12">
-        <v>668.43438095238093</v>
+        <v>668.43</v>
       </c>
       <c r="E12">
-        <v>350.48785714285708</v>
+        <v>350.49</v>
       </c>
       <c r="F12">
-        <v>1.3946799727390931</v>
+        <v>1.3947000000000001</v>
       </c>
       <c r="G12">
         <v>3.03</v>
       </c>
       <c r="H12">
-        <v>153.14002803610481</v>
+        <v>107.43529586641</v>
       </c>
       <c r="I12">
-        <v>89.250069240369882</v>
+        <v>89.250069240369896</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1478,28 +1497,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D13">
-        <v>798.7311428571428</v>
+        <v>798.73</v>
       </c>
       <c r="E13">
-        <v>417.64466666666669</v>
+        <v>417.64</v>
       </c>
       <c r="F13">
-        <v>1.441835312194548</v>
+        <v>1.4418</v>
       </c>
       <c r="G13">
         <v>3.08</v>
       </c>
       <c r="H13">
-        <v>153.90572817628529</v>
+        <v>107.97247234574201</v>
       </c>
       <c r="I13">
-        <v>90.27148523400794</v>
+        <v>90.271485234007898</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1507,28 +1526,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D14">
-        <v>1487.9692727272729</v>
+        <v>1487.97</v>
       </c>
       <c r="E14">
-        <v>707.06809090909087</v>
+        <v>707.07</v>
       </c>
       <c r="F14">
-        <v>1.378743243122023</v>
+        <v>1.3787</v>
       </c>
       <c r="G14">
         <v>3.23</v>
       </c>
       <c r="H14">
-        <v>154.5213510889904</v>
+        <v>108.40436223512501</v>
       </c>
       <c r="I14">
-        <v>94.290661155975329</v>
+        <v>94.2906611559753</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1536,28 +1555,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D15">
-        <v>1789.9661111111111</v>
+        <v>1789.97</v>
       </c>
       <c r="E15">
-        <v>768.1445555555556</v>
+        <v>768.14</v>
       </c>
       <c r="F15">
-        <v>1.4278693308613979</v>
+        <v>1.4278999999999999</v>
       </c>
       <c r="G15">
         <v>3.33</v>
       </c>
       <c r="H15">
-        <v>154.98491514225739</v>
+        <v>108.72957532183</v>
       </c>
       <c r="I15">
-        <v>96.919119313699127</v>
+        <v>96.919119313699099</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1565,28 +1584,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D16">
-        <v>1828.814090909091</v>
+        <v>1828.81</v>
       </c>
       <c r="E16">
-        <v>805.7409090909091</v>
+        <v>805.74</v>
       </c>
       <c r="F16">
-        <v>1.3677754304118399</v>
+        <v>1.3677999999999999</v>
       </c>
       <c r="G16">
         <v>3.43</v>
       </c>
       <c r="H16">
-        <v>155.44986988768409</v>
+        <v>109.055764047796</v>
       </c>
       <c r="I16">
-        <v>99.531010346135176</v>
+        <v>99.531010346135204</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1594,28 +1613,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D17">
-        <v>1573.5340000000001</v>
+        <v>1573.53</v>
       </c>
       <c r="E17">
-        <v>741.46494999999993</v>
+        <v>741.46</v>
       </c>
       <c r="F17">
-        <v>1.504587201794412</v>
+        <v>1.5045999999999999</v>
       </c>
       <c r="G17">
         <v>3.46</v>
       </c>
       <c r="H17">
-        <v>156.22711923712251</v>
+        <v>109.60104286803499</v>
       </c>
       <c r="I17">
-        <v>99.902033795346227</v>
+        <v>99.902033795346199</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1623,28 +1642,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D18">
-        <v>1644.651157894737</v>
+        <v>1644.65</v>
       </c>
       <c r="E18">
-        <v>731.09968421052633</v>
+        <v>731.1</v>
       </c>
       <c r="F18">
-        <v>1.3751394204118179</v>
+        <v>1.3751</v>
       </c>
       <c r="G18">
         <v>3.51</v>
       </c>
       <c r="H18">
-        <v>156.852027714071</v>
+        <v>110.039447039507</v>
       </c>
       <c r="I18">
-        <v>100.94193705572658</v>
+        <v>100.941937055727</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1652,28 +1671,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D19">
-        <v>1862.939318181818</v>
+        <v>1862.94</v>
       </c>
       <c r="E19">
-        <v>728.14709090909082</v>
+        <v>728.15</v>
       </c>
       <c r="F19">
-        <v>1.357811894361254</v>
+        <v>1.3577999999999999</v>
       </c>
       <c r="G19">
         <v>3.65</v>
       </c>
       <c r="H19">
-        <v>157.79313988035551</v>
+        <v>110.69968372174399</v>
       </c>
       <c r="I19">
-        <v>104.34205883032348</v>
+        <v>104.342058830323</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1681,28 +1700,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D20">
-        <v>1786.4335714285719</v>
+        <v>1786.43</v>
       </c>
       <c r="E20">
-        <v>655.37666666666667</v>
+        <v>655.38</v>
       </c>
       <c r="F20">
-        <v>1.353924062468419</v>
+        <v>1.3539000000000001</v>
       </c>
       <c r="G20">
         <v>3.69</v>
       </c>
       <c r="H20">
-        <v>158.2665192999965</v>
+        <v>111.031782772909</v>
       </c>
       <c r="I20">
-        <v>105.17002337750958</v>
+        <v>105.17002337751001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1710,28 +1729,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D21">
-        <v>1457.1070500000001</v>
+        <v>1457.11</v>
       </c>
       <c r="E21">
-        <v>562.87740000000008</v>
+        <v>562.88</v>
       </c>
       <c r="F21">
-        <v>1.321658526861361</v>
+        <v>1.3217000000000001</v>
       </c>
       <c r="G21">
         <v>3.73</v>
       </c>
       <c r="H21">
-        <v>158.74131885789649</v>
+        <v>111.364878121228</v>
       </c>
       <c r="I21">
-        <v>105.99210152688568</v>
+        <v>105.992101526886</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1739,28 +1758,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D22">
-        <v>1138.6053181818179</v>
+        <v>1138.6099999999999</v>
       </c>
       <c r="E22">
-        <v>500.98050000000001</v>
+        <v>500.98</v>
       </c>
       <c r="F22">
-        <v>1.340302011764134</v>
+        <v>1.3403</v>
       </c>
       <c r="G22">
         <v>3.77</v>
       </c>
       <c r="H22">
-        <v>159.37628413332811</v>
+        <v>111.810337633713</v>
       </c>
       <c r="I22">
-        <v>106.70193829410482</v>
+        <v>106.70193829410501</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1768,28 +1787,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D23">
-        <v>1038.6747272727271</v>
+        <v>1038.67</v>
       </c>
       <c r="E23">
-        <v>453.68290909090899</v>
+        <v>453.68</v>
       </c>
       <c r="F23">
-        <v>1.2345246062032349</v>
+        <v>1.2344999999999999</v>
       </c>
       <c r="G23">
         <v>3.81</v>
       </c>
       <c r="H23">
-        <v>160.33254183812801</v>
+        <v>112.481199659515</v>
       </c>
       <c r="I23">
-        <v>107.19090889689431</v>
+        <v>107.190908896894</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1797,28 +1816,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D24">
-        <v>900.20595238095245</v>
+        <v>900.21</v>
       </c>
       <c r="E24">
-        <v>410.88585714285711</v>
+        <v>410.89</v>
       </c>
       <c r="F24">
-        <v>1.1110363977510971</v>
+        <v>1.111</v>
       </c>
       <c r="G24">
         <v>3.84</v>
       </c>
       <c r="H24">
-        <v>161.61520217283299</v>
+        <v>113.381049256791</v>
       </c>
       <c r="I24">
-        <v>107.17751170793082</v>
+        <v>107.177511707931</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1826,28 +1845,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D25">
-        <v>820.55795238095243</v>
+        <v>820.56</v>
       </c>
       <c r="E25">
-        <v>389.23552380952378</v>
+        <v>389.24</v>
       </c>
       <c r="F25">
-        <v>1.223654795728635</v>
+        <v>1.2237</v>
       </c>
       <c r="G25">
         <v>3.84</v>
       </c>
       <c r="H25">
-        <v>162.74650858804279</v>
+        <v>114.174716601589</v>
       </c>
       <c r="I25">
-        <v>106.43248431770687</v>
+        <v>106.43248431770699</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1855,28 +1874,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D26">
-        <v>708.77761904761905</v>
+        <v>708.78</v>
       </c>
       <c r="E26">
-        <v>363.18238095238092</v>
+        <v>363.18</v>
       </c>
       <c r="F26">
-        <v>1.14581891341424</v>
+        <v>1.1457999999999999</v>
       </c>
       <c r="G26">
         <v>3.83</v>
       </c>
       <c r="H26">
-        <v>164.04848065674719</v>
+        <v>115.088114334401</v>
       </c>
       <c r="I26">
-        <v>105.31281387876608</v>
+        <v>105.31281387876599</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1884,28 +1903,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D27">
-        <v>725.7213684210526</v>
+        <v>725.72</v>
       </c>
       <c r="E27">
-        <v>368.41947368421052</v>
+        <v>368.42</v>
       </c>
       <c r="F27">
-        <v>1.158551833085284</v>
+        <v>1.1586000000000001</v>
       </c>
       <c r="G27">
         <v>3.81</v>
       </c>
       <c r="H27">
-        <v>165.36086850200121</v>
+        <v>116.00881924907701</v>
       </c>
       <c r="I27">
-        <v>103.9314261050237</v>
+        <v>103.931426105024</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1913,28 +1932,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D28">
-        <v>719.92086363636361</v>
+        <v>719.92</v>
       </c>
       <c r="E28">
-        <v>358.59609090909089</v>
+        <v>358.6</v>
       </c>
       <c r="F28">
-        <v>1.04431645461675</v>
+        <v>1.0443</v>
       </c>
       <c r="G28">
         <v>3.81</v>
       </c>
       <c r="H28">
-        <v>166.84911631851921</v>
+        <v>117.052898622318</v>
       </c>
       <c r="I28">
-        <v>103.00438662539516</v>
+        <v>103.004386625395</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1942,28 +1961,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D29">
-        <v>711.67221052631578</v>
+        <v>711.67</v>
       </c>
       <c r="E29">
-        <v>343.01405263157892</v>
+        <v>343.01</v>
       </c>
       <c r="F29">
-        <v>1.2592818243476951</v>
+        <v>1.2593000000000001</v>
       </c>
       <c r="G29">
         <v>3.8</v>
       </c>
       <c r="H29">
-        <v>168.5176074817044</v>
+        <v>118.223427608541</v>
       </c>
       <c r="I29">
-        <v>101.71686525207284</v>
+        <v>101.71686525207301</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1971,28 +1990,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D30">
-        <v>790.2707894736842</v>
+        <v>790.27</v>
       </c>
       <c r="E30">
-        <v>365.09647368421048</v>
+        <v>365.1</v>
       </c>
       <c r="F30">
-        <v>1.1872125551577779</v>
+        <v>1.1872</v>
       </c>
       <c r="G30">
         <v>3.85</v>
       </c>
       <c r="H30">
-        <v>170.53981877148479</v>
+        <v>119.64210873984401</v>
       </c>
       <c r="I30">
-        <v>101.83324610476403</v>
+        <v>101.833246104764</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -2000,28 +2019,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D31">
-        <v>704.27817391304347</v>
+        <v>704.28</v>
       </c>
       <c r="E31">
-        <v>321.53960869565219</v>
+        <v>321.54000000000002</v>
       </c>
       <c r="F31">
-        <v>1.3372835123955249</v>
+        <v>1.3372999999999999</v>
       </c>
       <c r="G31">
         <v>3.86</v>
       </c>
       <c r="H31">
-        <v>172.4157567779711</v>
+        <v>120.95817193598199</v>
       </c>
       <c r="I31">
-        <v>100.9868922281884</v>
+        <v>100.986892228188</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -2029,28 +2048,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D32">
-        <v>629.92104761904761</v>
+        <v>629.91999999999996</v>
       </c>
       <c r="E32">
-        <v>300.3308571428571</v>
+        <v>300.33</v>
       </c>
       <c r="F32">
-        <v>1.390221136440454</v>
+        <v>1.3902000000000001</v>
       </c>
       <c r="G32">
         <v>3.88</v>
       </c>
       <c r="H32">
-        <v>173.79508283219491</v>
+        <v>121.92583731147</v>
       </c>
       <c r="I32">
-        <v>100.70450433973059</v>
+        <v>100.704504339731</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2058,28 +2077,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D33">
-        <v>766.12029999999993</v>
+        <v>766.12</v>
       </c>
       <c r="E33">
-        <v>370.94490000000002</v>
+        <v>370.94</v>
       </c>
       <c r="F33">
-        <v>1.5918539026467671</v>
+        <v>1.5919000000000001</v>
       </c>
       <c r="G33">
         <v>3.9</v>
       </c>
       <c r="H33">
-        <v>175.01164841202029</v>
+        <v>122.77931817264999</v>
       </c>
       <c r="I33">
-        <v>100.51996000290477</v>
+        <v>100.51996000290499</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2087,28 +2106,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D34">
-        <v>804.75177272727274</v>
+        <v>804.75</v>
       </c>
       <c r="E34">
-        <v>387.93927272727268</v>
+        <v>387.94</v>
       </c>
       <c r="F34">
-        <v>1.6098486545875821</v>
+        <v>1.6097999999999999</v>
       </c>
       <c r="G34">
         <v>3.93</v>
       </c>
       <c r="H34">
-        <v>176.23672995090439</v>
+        <v>123.63877339985901</v>
       </c>
       <c r="I34">
-        <v>100.58906699549711</v>
+        <v>100.58906699549701</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2116,28 +2135,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D35">
-        <v>765.31190476190477</v>
+        <v>765.31</v>
       </c>
       <c r="E35">
-        <v>374.76985714285718</v>
+        <v>374.77</v>
       </c>
       <c r="F35">
-        <v>1.686758964614492</v>
+        <v>1.6868000000000001</v>
       </c>
       <c r="G35">
         <v>3.93</v>
       </c>
       <c r="H35">
-        <v>177.6466237905116</v>
+        <v>124.62788358705799</v>
       </c>
       <c r="I35">
-        <v>99.790741066961417</v>
+        <v>99.790741066961402</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2145,25 +2164,25 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D36">
-        <v>713.50945454545456</v>
+        <v>713.51</v>
       </c>
       <c r="E36">
-        <v>347.42854545454537</v>
+        <v>347.43</v>
       </c>
       <c r="F36">
-        <v>1.7964744833618289</v>
+        <v>1.7965</v>
       </c>
       <c r="G36">
         <v>3.94</v>
       </c>
       <c r="H36">
-        <v>178.89015015704521</v>
+        <v>125.50027877216699</v>
       </c>
       <c r="I36">
         <v>99.3492170086312</v>
@@ -2174,28 +2193,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D37">
-        <v>703.78899999999999</v>
+        <v>703.79</v>
       </c>
       <c r="E37">
-        <v>356.70009523809517</v>
+        <v>356.7</v>
       </c>
       <c r="F37">
-        <v>1.771250029115307</v>
+        <v>1.7713000000000001</v>
       </c>
       <c r="G37">
         <v>3.95</v>
       </c>
       <c r="H37">
-        <v>180.14238120814451</v>
+        <v>126.37878072357201</v>
       </c>
       <c r="I37">
-        <v>98.909009316533826</v>
+        <v>98.909009316533798</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2203,28 +2222,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D38">
-        <v>613.99549999999999</v>
+        <v>614</v>
       </c>
       <c r="E38">
-        <v>330.30504999999999</v>
+        <v>330.31</v>
       </c>
       <c r="F38">
-        <v>1.703713568441924</v>
+        <v>1.7037</v>
       </c>
       <c r="G38">
         <v>3.96</v>
       </c>
       <c r="H38">
-        <v>181.5835202578096</v>
+        <v>127.38981096936099</v>
       </c>
       <c r="I38">
-        <v>98.372432412465827</v>
+        <v>98.372432412465798</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2232,25 +2251,25 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D39">
-        <v>546.12209999999993</v>
+        <v>546.12</v>
       </c>
       <c r="E39">
-        <v>320.07049999999998</v>
+        <v>320.07</v>
       </c>
       <c r="F39">
-        <v>2.42189766542272</v>
+        <v>2.4218999999999999</v>
       </c>
       <c r="G39">
         <v>3.97</v>
       </c>
       <c r="H39">
-        <v>182.85460489961429</v>
+        <v>128.281539646146</v>
       </c>
       <c r="I39">
         <v>97.935300542036401</v>
@@ -2261,28 +2280,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D40">
-        <v>521.24154545454542</v>
+        <v>521.24</v>
       </c>
       <c r="E40">
-        <v>314.82722727272733</v>
+        <v>314.83</v>
       </c>
       <c r="F40">
-        <v>2.3362248783787032</v>
+        <v>2.3361999999999998</v>
       </c>
       <c r="G40">
         <v>3.98</v>
       </c>
       <c r="H40">
-        <v>184.3174417388112</v>
+        <v>129.30779196331599</v>
       </c>
       <c r="I40">
-        <v>97.402766821924573</v>
+        <v>97.402766821924601</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2290,28 +2309,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D41">
-        <v>497.09519999999998</v>
+        <v>497.1</v>
       </c>
       <c r="E41">
-        <v>303.24329999999998</v>
+        <v>303.24</v>
       </c>
       <c r="F41">
-        <v>2.163692332199135</v>
+        <v>2.1637</v>
       </c>
       <c r="G41">
         <v>4.13</v>
       </c>
       <c r="H41">
-        <v>185.6076638309828</v>
+        <v>130.212946507059</v>
       </c>
       <c r="I41">
-        <v>100.37112747814257</v>
+        <v>100.37112747814299</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2319,28 +2338,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D42">
-        <v>541.61905263157894</v>
+        <v>541.62</v>
       </c>
       <c r="E42">
-        <v>308.84668421052629</v>
+        <v>308.85000000000002</v>
       </c>
       <c r="F42">
-        <v>2.178610935120338</v>
+        <v>2.1785999999999999</v>
       </c>
       <c r="G42">
         <v>4.1500000000000004</v>
       </c>
       <c r="H42">
-        <v>186.90691747779971</v>
+        <v>131.12443713260799</v>
       </c>
       <c r="I42">
-        <v>100.1560935519864</v>
+        <v>100.156093551986</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2348,28 +2367,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D43">
-        <v>566.27543478260861</v>
+        <v>566.28</v>
       </c>
       <c r="E43">
-        <v>317.18839130434787</v>
+        <v>317.19</v>
       </c>
       <c r="F43">
-        <v>2.4236618658193891</v>
+        <v>2.4237000000000002</v>
       </c>
       <c r="G43">
         <v>4.1500000000000004</v>
       </c>
       <c r="H43">
-        <v>188.4021728176221</v>
+        <v>132.17343262966901</v>
       </c>
       <c r="I43">
-        <v>99.361203920621421</v>
+        <v>99.361203920621406</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2377,28 +2396,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D44">
-        <v>533.00964999999997</v>
+        <v>533.01</v>
       </c>
       <c r="E44">
-        <v>316.47055</v>
+        <v>316.47000000000003</v>
       </c>
       <c r="F44">
-        <v>2.186290008856338</v>
+        <v>2.1863000000000001</v>
       </c>
       <c r="G44">
         <v>4.3</v>
       </c>
       <c r="H44">
-        <v>189.9093902001631</v>
+        <v>133.230820090706</v>
       </c>
       <c r="I44">
-        <v>102.13548882641805</v>
+        <v>102.135488826418</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2406,28 +2425,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D45">
-        <v>580.76128571428569</v>
+        <v>580.76</v>
       </c>
       <c r="E45">
-        <v>324.35257142857142</v>
+        <v>324.35000000000002</v>
       </c>
       <c r="F45">
-        <v>2.338864624471499</v>
+        <v>2.3389000000000002</v>
       </c>
       <c r="G45">
         <v>4.29</v>
       </c>
       <c r="H45">
-        <v>191.23875593156421</v>
+        <v>134.16343583134099</v>
       </c>
       <c r="I45">
-        <v>101.18963697497369</v>
+        <v>101.18963697497399</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2435,28 +2454,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D46">
-        <v>604.61927272727269</v>
+        <v>604.62</v>
       </c>
       <c r="E46">
-        <v>332.11613636363637</v>
+        <v>332.12</v>
       </c>
       <c r="F46">
-        <v>2.29441622776582</v>
+        <v>2.2944</v>
       </c>
       <c r="G46">
         <v>4.2699999999999996</v>
       </c>
       <c r="H46">
-        <v>192.5774272230851</v>
+        <v>135.102579882161</v>
       </c>
       <c r="I46">
-        <v>100.01776605327686</v>
+        <v>100.017766053277</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2464,28 +2483,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D47">
-        <v>595.05759999999998</v>
+        <v>595.05999999999995</v>
       </c>
       <c r="E47">
-        <v>318.8811</v>
+        <v>318.88</v>
       </c>
       <c r="F47">
-        <v>2.4784050006636051</v>
+        <v>2.4784000000000002</v>
       </c>
       <c r="G47">
         <v>4.34</v>
       </c>
       <c r="H47">
-        <v>194.11804664086981</v>
+        <v>136.183400521218</v>
       </c>
       <c r="I47">
-        <v>100.85059678804265</v>
+        <v>100.85059678804301</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2493,28 +2512,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D48">
-        <v>718.99199999999996</v>
+        <v>718.99</v>
       </c>
       <c r="E48">
-        <v>367.83478260869572</v>
+        <v>367.83</v>
       </c>
       <c r="F48">
-        <v>2.2461615886540689</v>
+        <v>2.2462</v>
       </c>
       <c r="G48">
         <v>4.43</v>
       </c>
       <c r="H48">
-        <v>195.6709910139968</v>
+        <v>137.27286772538801</v>
       </c>
       <c r="I48">
-        <v>102.12496885995648</v>
+        <v>102.124968859956</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2522,28 +2541,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D49">
-        <v>877.82047619047614</v>
+        <v>877.82</v>
       </c>
       <c r="E49">
-        <v>422.41157142857139</v>
+        <v>422.41</v>
       </c>
       <c r="F49">
-        <v>2.640606704855418</v>
+        <v>2.6406000000000001</v>
       </c>
       <c r="G49">
         <v>4.43</v>
       </c>
       <c r="H49">
-        <v>197.23635894210869</v>
+        <v>138.37105066719101</v>
       </c>
       <c r="I49">
-        <v>101.31445323408381</v>
+        <v>101.314453234084</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2551,28 +2570,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D50">
-        <v>904.8691500000001</v>
+        <v>904.87</v>
       </c>
       <c r="E50">
-        <v>420.78115000000003</v>
+        <v>420.78</v>
       </c>
       <c r="F50">
-        <v>2.6209035804414951</v>
+        <v>2.6208999999999998</v>
       </c>
       <c r="G50">
         <v>4.4800000000000004</v>
       </c>
       <c r="H50">
-        <v>198.41977709576139</v>
+        <v>139.20127697119401</v>
       </c>
       <c r="I50">
-        <v>101.84687596513371</v>
+        <v>101.846875965134</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2580,28 +2599,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D51">
-        <v>893.04089999999997</v>
+        <v>893.04</v>
       </c>
       <c r="E51">
-        <v>402.81060000000002</v>
+        <v>402.81</v>
       </c>
       <c r="F51">
-        <v>2.6220016542597189</v>
+        <v>2.6219999999999999</v>
       </c>
       <c r="G51">
         <v>4.62</v>
       </c>
       <c r="H51">
-        <v>199.61029575833601</v>
+        <v>140.03648463302099</v>
       </c>
       <c r="I51">
-        <v>104.40317180819495</v>
+        <v>104.403171808195</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2609,28 +2628,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D52">
-        <v>926.80647619047625</v>
+        <v>926.81</v>
       </c>
       <c r="E52">
-        <v>397.61057142857152</v>
+        <v>397.61</v>
       </c>
       <c r="F52">
-        <v>2.7104712170807481</v>
+        <v>2.7105000000000001</v>
       </c>
       <c r="G52">
         <v>4.7300000000000004</v>
       </c>
       <c r="H52">
-        <v>201.20717812440259</v>
+        <v>141.156776510085</v>
       </c>
       <c r="I52">
-        <v>106.04063652098412</v>
+        <v>106.04063652098399</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2638,28 +2657,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D53">
-        <v>850.91020000000003</v>
+        <v>850.91</v>
       </c>
       <c r="E53">
-        <v>394.0702</v>
+        <v>394.07</v>
       </c>
       <c r="F53">
-        <v>2.7488439649905638</v>
+        <v>2.7488000000000001</v>
       </c>
       <c r="G53">
         <v>4.78</v>
       </c>
       <c r="H53">
-        <v>203.01804272752219</v>
+        <v>142.42718749867601</v>
       </c>
       <c r="I53">
-        <v>106.20572198423577</v>
+        <v>106.20572198423601</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2667,28 +2686,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D54">
-        <v>822.43399999999997</v>
+        <v>822.43</v>
       </c>
       <c r="E54">
-        <v>364.76400000000001</v>
+        <v>364.76</v>
       </c>
       <c r="F54">
-        <v>2.5577177664740698</v>
+        <v>2.5577000000000001</v>
       </c>
       <c r="G54">
         <v>4.71</v>
       </c>
       <c r="H54">
-        <v>204.43916902661491</v>
+        <v>143.424177811167</v>
       </c>
       <c r="I54">
-        <v>103.92294743194095</v>
+        <v>103.922947431941</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2696,28 +2715,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D55">
-        <v>823.11618181818187</v>
+        <v>823.12</v>
       </c>
       <c r="E55">
-        <v>331.65359090909089</v>
+        <v>331.65</v>
       </c>
       <c r="F55">
-        <v>2.2555435009574909</v>
+        <v>2.2555000000000001</v>
       </c>
       <c r="G55">
         <v>4.92</v>
       </c>
       <c r="H55">
-        <v>206.2791215478544</v>
+        <v>144.71499541146699</v>
       </c>
       <c r="I55">
-        <v>107.58816119155823</v>
+        <v>107.588161191558</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2725,28 +2744,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D56">
-        <v>967.30514999999991</v>
+        <v>967.31</v>
       </c>
       <c r="E56">
-        <v>346.93369999999999</v>
+        <v>346.93</v>
       </c>
       <c r="F56">
-        <v>1.9038940394267629</v>
+        <v>1.9038999999999999</v>
       </c>
       <c r="G56">
         <v>5.07</v>
       </c>
       <c r="H56">
-        <v>207.9293545202373</v>
+        <v>145.872715374759</v>
       </c>
       <c r="I56">
-        <v>109.98838100908191</v>
+        <v>109.988381009082</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2754,28 +2773,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D57">
-        <v>1089.3252727272729</v>
+        <v>1089.33</v>
       </c>
       <c r="E57">
-        <v>376.11268181818178</v>
+        <v>376.11</v>
       </c>
       <c r="F57">
-        <v>2.1415381401955171</v>
+        <v>2.1415000000000002</v>
       </c>
       <c r="G57">
         <v>5.9</v>
       </c>
       <c r="H57">
-        <v>209.59278935639909</v>
+        <v>147.039697097757</v>
       </c>
       <c r="I57">
-        <v>126.97854011176528</v>
+        <v>126.978540111765</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2783,28 +2802,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C58" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D58">
-        <v>1128.6606666666671</v>
+        <v>1128.6600000000001</v>
       </c>
       <c r="E58">
-        <v>390.2235714285714</v>
+        <v>390.22</v>
       </c>
       <c r="F58">
-        <v>1.9853477735916281</v>
+        <v>1.9853000000000001</v>
       </c>
       <c r="G58">
         <v>5.93</v>
       </c>
       <c r="H58">
-        <v>211.05993888189391</v>
+        <v>148.068974977441</v>
       </c>
       <c r="I58">
-        <v>126.7370344643038</v>
+        <v>126.737034464304</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2812,28 +2831,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D59">
-        <v>1091.756095238095</v>
+        <v>1091.76</v>
       </c>
       <c r="E59">
-        <v>365.89947619047621</v>
+        <v>365.9</v>
       </c>
       <c r="F59">
-        <v>1.8433711617102539</v>
+        <v>1.8433999999999999</v>
       </c>
       <c r="G59">
         <v>6.29</v>
       </c>
       <c r="H59">
-        <v>212.74841839294911</v>
+        <v>149.25352677726099</v>
       </c>
       <c r="I59">
-        <v>133.36410683845773</v>
+        <v>133.36410683845801</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2841,28 +2860,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D60">
-        <v>1038.97347826087</v>
+        <v>1038.97</v>
       </c>
       <c r="E60">
-        <v>329.89573913043478</v>
+        <v>329.9</v>
       </c>
       <c r="F60">
-        <v>1.8038162299223801</v>
+        <v>1.8038000000000001</v>
       </c>
       <c r="G60">
         <v>6.35</v>
       </c>
       <c r="H60">
-        <v>214.66315415848561</v>
+        <v>150.59680851825601</v>
       </c>
       <c r="I60">
-        <v>133.43534239920317</v>
+        <v>133.43534239920299</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2870,28 +2889,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C61" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D61">
-        <v>917.68121052631579</v>
+        <v>917.68</v>
       </c>
       <c r="E61">
-        <v>313.25736842105272</v>
+        <v>313.26</v>
       </c>
       <c r="F61">
-        <v>1.68784684625814</v>
+        <v>1.6878</v>
       </c>
       <c r="G61">
         <v>6.28</v>
       </c>
       <c r="H61">
-        <v>216.59512254591189</v>
+        <v>151.95217979492099</v>
       </c>
       <c r="I61">
-        <v>130.78731577487585</v>
+        <v>130.78731577487599</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2899,28 +2918,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D62">
-        <v>888.63961904761914</v>
+        <v>888.64</v>
       </c>
       <c r="E62">
-        <v>301.24161904761911</v>
+        <v>301.24</v>
       </c>
       <c r="F62">
-        <v>1.669391823583031</v>
+        <v>1.6694</v>
       </c>
       <c r="G62">
         <v>6.32</v>
       </c>
       <c r="H62">
-        <v>218.32788352627921</v>
+        <v>153.16779723328</v>
       </c>
       <c r="I62">
-        <v>130.57575000271956</v>
+        <v>130.57575000272001</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2928,28 +2947,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D63">
-        <v>1197.1325999999999</v>
+        <v>1197.1300000000001</v>
       </c>
       <c r="E63">
-        <v>323.42214999999999</v>
+        <v>323.42</v>
       </c>
       <c r="F63">
-        <v>1.6868282668143539</v>
+        <v>1.6868000000000001</v>
       </c>
       <c r="G63">
         <v>6.42</v>
       </c>
       <c r="H63">
-        <v>220.29283447801569</v>
+        <v>154.54630740837899</v>
       </c>
       <c r="I63">
-        <v>131.45869375265954</v>
+        <v>131.45869375266</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2957,28 +2976,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D64">
-        <v>1036.4516000000001</v>
+        <v>1036.45</v>
       </c>
       <c r="E64">
-        <v>299.51835</v>
+        <v>299.52</v>
       </c>
       <c r="F64">
-        <v>1.838981701734582</v>
+        <v>1.839</v>
       </c>
       <c r="G64">
         <v>6.78</v>
       </c>
       <c r="H64">
-        <v>222.49576282279591</v>
+        <v>156.09177048246301</v>
       </c>
       <c r="I64">
-        <v>137.45565276256622</v>
+        <v>137.45565276256599</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2986,28 +3005,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D65">
-        <v>1057.799238095238</v>
+        <v>1057.8</v>
       </c>
       <c r="E65">
-        <v>287.99028571428568</v>
+        <v>287.99</v>
       </c>
       <c r="F65">
-        <v>1.762382782079787</v>
+        <v>1.7624</v>
       </c>
       <c r="G65">
         <v>7.89</v>
       </c>
       <c r="H65">
-        <v>224.9432162138466</v>
+        <v>157.80877995777001</v>
       </c>
       <c r="I65">
-        <v>158.21904482793218</v>
+        <v>158.21904482793201</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3015,28 +3034,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D66">
-        <v>1114.3788421052629</v>
+        <v>1114.3800000000001</v>
       </c>
       <c r="E66">
-        <v>302.17200000000003</v>
+        <v>302.17</v>
       </c>
       <c r="F66">
-        <v>1.8314094381100401</v>
+        <v>1.8313999999999999</v>
       </c>
       <c r="G66">
         <v>7.82</v>
       </c>
       <c r="H66">
-        <v>226.06793229491589</v>
+        <v>158.59782385755901</v>
       </c>
       <c r="I66">
-        <v>156.03515130991809</v>
+        <v>156.03515130991801</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -3044,28 +3063,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D67">
-        <v>1206.7547</v>
+        <v>1206.75</v>
       </c>
       <c r="E67">
-        <v>316.86214999999999</v>
+        <v>316.86</v>
       </c>
       <c r="F67">
-        <v>1.913987955367201</v>
+        <v>1.9139999999999999</v>
       </c>
       <c r="G67">
         <v>8.3800000000000008</v>
       </c>
       <c r="H67">
-        <v>227.65040782098021</v>
+        <v>159.70800862456201</v>
       </c>
       <c r="I67">
-        <v>166.0466971578889</v>
+        <v>166.04669715788901</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -3073,28 +3092,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D68">
-        <v>1223.0598181818179</v>
+        <v>1223.06</v>
       </c>
       <c r="E68">
-        <v>316.34163636363633</v>
+        <v>316.33999999999997</v>
       </c>
       <c r="F68">
-        <v>1.7586069052648221</v>
+        <v>1.7585999999999999</v>
       </c>
       <c r="G68">
         <v>9.3699999999999992</v>
       </c>
       <c r="H68">
-        <v>229.2439606757271</v>
+        <v>160.82596468493401</v>
       </c>
       <c r="I68">
-        <v>184.37258431663545</v>
+        <v>184.372584316635</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -3102,28 +3121,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C69" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D69">
-        <v>1174.2063636363639</v>
+        <v>1174.21</v>
       </c>
       <c r="E69">
-        <v>313.93945454545451</v>
+        <v>313.94</v>
       </c>
       <c r="F69">
-        <v>1.420147142501418</v>
+        <v>1.4200999999999999</v>
       </c>
       <c r="G69">
         <v>8.75</v>
       </c>
       <c r="H69">
-        <v>230.84866840045709</v>
+        <v>161.95174643772799</v>
       </c>
       <c r="I69">
-        <v>170.97607174226098</v>
+        <v>170.97607174226101</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -3131,28 +3150,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D70">
-        <v>1203.8187499999999</v>
+        <v>1203.82</v>
       </c>
       <c r="E70">
-        <v>370.81079999999997</v>
+        <v>370.81</v>
       </c>
       <c r="F70">
-        <v>1.7441265126118899</v>
+        <v>1.7441</v>
       </c>
       <c r="G70">
         <v>8</v>
       </c>
       <c r="H70">
-        <v>232.69545774766081</v>
+        <v>163.24736040923</v>
       </c>
       <c r="I70">
-        <v>155.08033718118912</v>
+        <v>155.08033718118901</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -3160,28 +3179,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D71">
-        <v>1138.0431818181819</v>
+        <v>1138.04</v>
       </c>
       <c r="E71">
-        <v>360.93231818181818</v>
+        <v>360.93</v>
       </c>
       <c r="F71">
-        <v>1.679015908158062</v>
+        <v>1.679</v>
       </c>
       <c r="G71">
         <v>8.48</v>
       </c>
       <c r="H71">
-        <v>234.7897168673897</v>
+        <v>164.71658665291301</v>
       </c>
       <c r="I71">
-        <v>162.91888742523338</v>
+        <v>162.91888742523301</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -3189,28 +3208,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D72">
-        <v>1067.5389090909091</v>
+        <v>1067.54</v>
       </c>
       <c r="E72">
-        <v>365.34036363636358</v>
+        <v>365.34</v>
       </c>
       <c r="F72">
-        <v>1.8688059773886549</v>
+        <v>1.8688</v>
       </c>
       <c r="G72">
         <v>9.1999999999999993</v>
       </c>
       <c r="H72">
-        <v>236.66803460232879</v>
+        <v>166.03431934613701</v>
       </c>
       <c r="I72">
-        <v>175.34883249009653</v>
+        <v>175.34883249009701</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -3218,28 +3237,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C73" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D73">
-        <v>1063.5463999999999</v>
+        <v>1063.55</v>
       </c>
       <c r="E73">
-        <v>362.78345000000002</v>
+        <v>362.78</v>
       </c>
       <c r="F73">
-        <v>1.771609278972289</v>
+        <v>1.7716000000000001</v>
       </c>
       <c r="G73">
         <v>9.43</v>
       </c>
       <c r="H73">
-        <v>238.56137887914741</v>
+        <v>167.36259390090601</v>
       </c>
       <c r="I73">
-        <v>178.30610446661603</v>
+        <v>178.30610446661601</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3247,28 +3266,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C74" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D74">
-        <v>927.55563636363649</v>
+        <v>927.56</v>
       </c>
       <c r="E74">
-        <v>355.88213636363639</v>
+        <v>355.88</v>
       </c>
       <c r="F74">
-        <v>1.9764988177265139</v>
+        <v>1.9764999999999999</v>
       </c>
       <c r="G74">
         <v>9.8699999999999992</v>
       </c>
       <c r="H74">
-        <v>240.7084312890598</v>
+        <v>168.86885724601399</v>
       </c>
       <c r="I74">
-        <v>184.96114514286589</v>
+        <v>184.961145142866</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3276,28 +3295,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D75">
-        <v>820.55836842105271</v>
+        <v>820.56</v>
       </c>
       <c r="E75">
-        <v>366.32710526315788</v>
+        <v>366.33</v>
       </c>
       <c r="F75">
-        <v>1.847188757950742</v>
+        <v>1.8472</v>
       </c>
       <c r="G75">
         <v>9.5299999999999994</v>
       </c>
       <c r="H75">
-        <v>242.8748071706612</v>
+        <v>170.38867696122799</v>
       </c>
       <c r="I75">
-        <v>176.99666659753325</v>
+        <v>176.99666659753299</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3305,28 +3324,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D76">
-        <v>803.63319047619041</v>
+        <v>803.63</v>
       </c>
       <c r="E76">
-        <v>360.24747619047622</v>
+        <v>360.25</v>
       </c>
       <c r="F76">
-        <v>1.6809167892733861</v>
+        <v>1.6809000000000001</v>
       </c>
       <c r="G76">
         <v>9.9499999999999993</v>
       </c>
       <c r="H76">
-        <v>246.27505447105051</v>
+        <v>172.77411843868501</v>
       </c>
       <c r="I76">
-        <v>182.2457093498426</v>
+        <v>182.245709349843</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -3334,28 +3353,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D77">
-        <v>931.61990476190476</v>
+        <v>931.62</v>
       </c>
       <c r="E77">
-        <v>373.38323809523808</v>
+        <v>373.38</v>
       </c>
       <c r="F77">
-        <v>1.462483957259084</v>
+        <v>1.4624999999999999</v>
       </c>
       <c r="G77">
         <v>11.15</v>
       </c>
       <c r="H77">
-        <v>255.14095643200841</v>
+        <v>178.993986702478</v>
       </c>
       <c r="I77">
-        <v>197.12846658492705</v>
+        <v>197.128466584927</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3363,28 +3382,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D78">
-        <v>970.8811578947367</v>
+        <v>970.88</v>
       </c>
       <c r="E78">
-        <v>389.47426315789482</v>
+        <v>389.47</v>
       </c>
       <c r="F78">
-        <v>1.3849818186576139</v>
+        <v>1.385</v>
       </c>
       <c r="G78">
         <v>11.2</v>
       </c>
       <c r="H78">
-        <v>263.81574895069662</v>
+        <v>185.079782250362</v>
       </c>
       <c r="I78">
-        <v>191.50140303676633</v>
+        <v>191.50140303676599</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -3392,28 +3411,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D79">
-        <v>879.91095238095238</v>
+        <v>879.91</v>
       </c>
       <c r="E79">
-        <v>354.12442857142861</v>
+        <v>354.12</v>
       </c>
       <c r="F79">
-        <v>1.5262876914678489</v>
+        <v>1.5263</v>
       </c>
       <c r="G79">
         <v>10.7</v>
       </c>
       <c r="H79">
-        <v>270.67495842341481</v>
+        <v>189.891856588872</v>
       </c>
       <c r="I79">
-        <v>178.31601682099344</v>
+        <v>178.31601682099301</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3421,28 +3440,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C80" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D80">
-        <v>787.55480952380958</v>
+        <v>787.55</v>
       </c>
       <c r="E80">
-        <v>325.15152380952378</v>
+        <v>325.14999999999998</v>
       </c>
       <c r="F80">
-        <v>1.401645590676162</v>
+        <v>1.4016</v>
       </c>
       <c r="G80">
         <v>10.45</v>
       </c>
       <c r="H80">
-        <v>275.54710767503627</v>
+        <v>193.30991000747099</v>
       </c>
       <c r="I80">
-        <v>171.07048599777656</v>
+        <v>171.07048599777701</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -3450,28 +3469,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D81">
-        <v>797.97552380952379</v>
+        <v>797.98</v>
       </c>
       <c r="E81">
-        <v>319.45347619047618</v>
+        <v>319.45</v>
       </c>
       <c r="F81">
-        <v>1.5120710396795261</v>
+        <v>1.5121</v>
       </c>
       <c r="G81">
         <v>11.3</v>
       </c>
       <c r="H81">
-        <v>279.40476718248681</v>
+        <v>196.01624874757599</v>
       </c>
       <c r="I81">
-        <v>182.43127240403496</v>
+        <v>182.43127240403501</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -3479,28 +3498,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D82">
-        <v>763.00409523809526</v>
+        <v>763</v>
       </c>
       <c r="E82">
-        <v>303.67576190476188</v>
+        <v>303.68</v>
       </c>
       <c r="F82">
-        <v>1.6997180023594509</v>
+        <v>1.6997</v>
       </c>
       <c r="G82">
         <v>12.05</v>
       </c>
       <c r="H82">
-        <v>283.03702915585899</v>
+        <v>198.56445998129399</v>
       </c>
       <c r="I82">
-        <v>192.04298390556582</v>
+        <v>192.04298390556599</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -3508,25 +3527,25 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C83" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D83">
-        <v>651.2329545454545</v>
+        <v>651.23</v>
       </c>
       <c r="E83">
-        <v>297.11786363636361</v>
+        <v>297.12</v>
       </c>
       <c r="F83">
-        <v>1.872186275579709</v>
+        <v>1.8722000000000001</v>
       </c>
       <c r="G83">
         <v>12.6</v>
       </c>
       <c r="H83">
-        <v>286.99954756404111</v>
+        <v>201.344362421032</v>
       </c>
       <c r="I83">
         <v>198.035928307441</v>
@@ -3537,28 +3556,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D84">
-        <v>760.76514285714279</v>
+        <v>760.77</v>
       </c>
       <c r="E84">
-        <v>320.68928571428569</v>
+        <v>320.69</v>
       </c>
       <c r="F84">
-        <v>1.8208873309563509</v>
+        <v>1.8209</v>
       </c>
       <c r="G84">
         <v>13.95</v>
       </c>
       <c r="H84">
-        <v>290.73054168237371</v>
+        <v>203.96183913250599</v>
       </c>
       <c r="I84">
-        <v>216.44033907525991</v>
+        <v>216.44033907526</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -3566,28 +3585,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D85">
-        <v>718.74061904761902</v>
+        <v>718.74</v>
       </c>
       <c r="E85">
-        <v>322.79757142857142</v>
+        <v>322.8</v>
       </c>
       <c r="F85">
-        <v>1.705600851874292</v>
+        <v>1.7056</v>
       </c>
       <c r="G85">
         <v>15.6</v>
       </c>
       <c r="H85">
-        <v>294.80076926592687</v>
+        <v>206.81730488036101</v>
       </c>
       <c r="I85">
-        <v>238.69902296692572</v>
+        <v>238.69902296692601</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3595,28 +3614,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D86">
-        <v>759.33290909090908</v>
+        <v>759.33</v>
       </c>
       <c r="E86">
-        <v>360.86036363636362</v>
+        <v>360.86</v>
       </c>
       <c r="F86">
-        <v>1.6466781670144071</v>
+        <v>1.6467000000000001</v>
       </c>
       <c r="G86">
         <v>14.18</v>
       </c>
       <c r="H86">
-        <v>298.33837849711801</v>
+        <v>209.29911253892499</v>
       </c>
       <c r="I86">
-        <v>214.39850927783311</v>
+        <v>214.398509277833</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -3624,28 +3643,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C87" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D87">
-        <v>674.19127777777771</v>
+        <v>674.19</v>
       </c>
       <c r="E87">
-        <v>359.90433333333328</v>
+        <v>359.9</v>
       </c>
       <c r="F87">
-        <v>1.602982404151861</v>
+        <v>1.603</v>
       </c>
       <c r="G87">
         <v>13</v>
       </c>
       <c r="H87">
-        <v>301.62010066058622</v>
+        <v>211.60140277685301</v>
       </c>
       <c r="I87">
-        <v>194.41856228955612</v>
+        <v>194.41856228955601</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -3653,28 +3672,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D88">
-        <v>745.33086363636357</v>
+        <v>745.33</v>
       </c>
       <c r="E88">
-        <v>403.47427272727271</v>
+        <v>403.47</v>
       </c>
       <c r="F88">
-        <v>1.635693694594414</v>
+        <v>1.6356999999999999</v>
       </c>
       <c r="G88">
         <v>13.7</v>
       </c>
       <c r="H88">
-        <v>304.63630166719207</v>
+        <v>213.71741680462199</v>
       </c>
       <c r="I88">
-        <v>202.8586674308392</v>
+        <v>202.85866743083901</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -3682,28 +3701,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D89">
-        <v>732.21260000000007</v>
+        <v>732.21</v>
       </c>
       <c r="E89">
-        <v>436.98585000000003</v>
+        <v>436.99</v>
       </c>
       <c r="F89">
-        <v>1.8263827843473679</v>
+        <v>1.8264</v>
       </c>
       <c r="G89">
         <v>13.5</v>
       </c>
       <c r="H89">
-        <v>307.98730098553119</v>
+        <v>216.068308389473</v>
       </c>
       <c r="I89">
-        <v>197.72228192916819</v>
+        <v>197.72228192916799</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -3711,28 +3730,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C90" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D90">
-        <v>684.13084210526313</v>
+        <v>684.13</v>
       </c>
       <c r="E90">
-        <v>414.08178947368418</v>
+        <v>414.08</v>
       </c>
       <c r="F90">
-        <v>1.6532339182167539</v>
+        <v>1.6532</v>
       </c>
       <c r="G90">
         <v>12.93</v>
       </c>
       <c r="H90">
-        <v>310.75918669440102</v>
+        <v>218.01292316497799</v>
       </c>
       <c r="I90">
-        <v>187.68484420542117</v>
+        <v>187.684844205421</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3740,28 +3759,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D91">
-        <v>593.1705454545455</v>
+        <v>593.16999999999996</v>
       </c>
       <c r="E91">
-        <v>410.21100000000001</v>
+        <v>410.21</v>
       </c>
       <c r="F91">
-        <v>1.8635460477543631</v>
+        <v>1.8634999999999999</v>
       </c>
       <c r="G91">
         <v>12.52</v>
       </c>
       <c r="H91">
-        <v>314.79905612142818</v>
+        <v>220.84709116612299</v>
       </c>
       <c r="I91">
-        <v>179.40129052799861</v>
+        <v>179.40129052799901</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3769,28 +3788,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C92" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D92">
-        <v>603.44909523809531</v>
+        <v>603.45000000000005</v>
       </c>
       <c r="E92">
-        <v>391.01080952380948</v>
+        <v>391.01</v>
       </c>
       <c r="F92">
-        <v>1.896234972352087</v>
+        <v>1.8962000000000001</v>
       </c>
       <c r="G92">
         <v>12.6</v>
       </c>
       <c r="H92">
-        <v>318.26184573876378</v>
+        <v>223.27640916895001</v>
       </c>
       <c r="I92">
-        <v>178.58320934992898</v>
+        <v>178.58320934992901</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3798,28 +3817,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C93" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D93">
-        <v>596.21845000000008</v>
+        <v>596.22</v>
       </c>
       <c r="E93">
-        <v>376.39519999999999</v>
+        <v>376.4</v>
       </c>
       <c r="F93">
-        <v>2.0906344709805409</v>
+        <v>2.0905999999999998</v>
       </c>
       <c r="G93">
         <v>12.55</v>
       </c>
       <c r="H93">
-        <v>321.44446419615139</v>
+        <v>225.50917326063899</v>
       </c>
       <c r="I93">
-        <v>176.11341170372535</v>
+        <v>176.11341170372501</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3827,28 +3846,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C94" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D94">
-        <v>593.42072727272728</v>
+        <v>593.41999999999996</v>
       </c>
       <c r="E94">
-        <v>398.0392727272727</v>
+        <v>398.04</v>
       </c>
       <c r="F94">
-        <v>1.9372752350571321</v>
+        <v>1.9373</v>
       </c>
       <c r="G94">
         <v>13.3</v>
       </c>
       <c r="H94">
-        <v>324.65890883811289</v>
+        <v>227.764264993246</v>
       </c>
       <c r="I94">
-        <v>184.79021542815249</v>
+        <v>184.790215428153</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -3856,28 +3875,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C95" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D95">
-        <v>603.20013636363637</v>
+        <v>603.20000000000005</v>
       </c>
       <c r="E95">
-        <v>415.2400909090909</v>
+        <v>415.24</v>
       </c>
       <c r="F95">
-        <v>2.0366471266482939</v>
+        <v>2.0366</v>
       </c>
       <c r="G95">
         <v>14.79</v>
       </c>
       <c r="H95">
-        <v>328.8794746530084</v>
+        <v>230.725200438158</v>
       </c>
       <c r="I95">
-        <v>202.85516007558698</v>
+        <v>202.85516007558701</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3885,28 +3904,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D96">
-        <v>589.99138095238095</v>
+        <v>589.99</v>
       </c>
       <c r="E96">
-        <v>451.98157142857139</v>
+        <v>451.98</v>
       </c>
       <c r="F96">
-        <v>1.9172549725043651</v>
+        <v>1.9173</v>
       </c>
       <c r="G96">
         <v>15.32</v>
       </c>
       <c r="H96">
-        <v>332.82602834884449</v>
+        <v>233.49390284341601</v>
       </c>
       <c r="I96">
-        <v>207.6328849183692</v>
+        <v>207.632884918369</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -3914,28 +3933,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C97" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D97">
-        <v>561.41399999999999</v>
+        <v>561.41</v>
       </c>
       <c r="E97">
-        <v>470.60680952380949</v>
+        <v>470.61</v>
       </c>
       <c r="F97">
-        <v>1.777935535542563</v>
+        <v>1.7779</v>
       </c>
       <c r="G97">
         <v>15.84</v>
       </c>
       <c r="H97">
-        <v>336.81994068903049</v>
+        <v>236.295829677537</v>
       </c>
       <c r="I97">
-        <v>212.13485801627004</v>
+        <v>212.13485801626999</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3943,28 +3962,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C98" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D98">
-        <v>555.1966666666666</v>
+        <v>555.20000000000005</v>
       </c>
       <c r="E98">
-        <v>477.74928571428569</v>
+        <v>477.75</v>
       </c>
       <c r="F98">
-        <v>1.908506718702373</v>
+        <v>1.9085000000000001</v>
       </c>
       <c r="G98">
         <v>15.6</v>
       </c>
       <c r="H98">
-        <v>340.52496003660991</v>
+        <v>238.89508380398999</v>
       </c>
       <c r="I98">
-        <v>206.64757022836005</v>
+        <v>206.64757022836</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -3972,28 +3991,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C99" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D99">
-        <v>486.12052631578939</v>
+        <v>486.12</v>
       </c>
       <c r="E99">
-        <v>462.69021052631581</v>
+        <v>462.69</v>
       </c>
       <c r="F99">
-        <v>1.748936835665043</v>
+        <v>1.7488999999999999</v>
       </c>
       <c r="G99">
         <v>14.59</v>
       </c>
       <c r="H99">
-        <v>347.33545923734209</v>
+        <v>243.67298548007</v>
       </c>
       <c r="I99">
-        <v>189.47888698037792</v>
+        <v>189.47888698037801</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -4001,28 +4020,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C100" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D100">
-        <v>478.07922727272728</v>
+        <v>478.08</v>
       </c>
       <c r="E100">
-        <v>494.12545454545449</v>
+        <v>494.13</v>
       </c>
       <c r="F100">
-        <v>1.7974913967000721</v>
+        <v>1.7975000000000001</v>
       </c>
       <c r="G100">
         <v>14.17</v>
       </c>
       <c r="H100">
-        <v>360.8815421475984</v>
+        <v>253.17623191379201</v>
       </c>
       <c r="I100">
-        <v>177.11683206963747</v>
+        <v>177.11683206963701</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -4030,28 +4049,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D101">
-        <v>485.88005263157891</v>
+        <v>485.88</v>
       </c>
       <c r="E101">
-        <v>546.0472631578948</v>
+        <v>546.04999999999995</v>
       </c>
       <c r="F101">
-        <v>3.1378444917301982</v>
+        <v>3.1377999999999999</v>
       </c>
       <c r="G101">
         <v>13.87</v>
       </c>
       <c r="H101">
-        <v>375.6776853756499</v>
+        <v>263.55645742225801</v>
       </c>
       <c r="I101">
-        <v>166.53890969921784</v>
+        <v>166.53890969921801</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -4059,28 +4078,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D102">
-        <v>470.88004999999998</v>
+        <v>470.88</v>
       </c>
       <c r="E102">
-        <v>566.61590000000001</v>
+        <v>566.62</v>
       </c>
       <c r="F102">
-        <v>2.8618604040847049</v>
+        <v>2.8618999999999999</v>
       </c>
       <c r="G102">
         <v>15.21</v>
       </c>
       <c r="H102">
-        <v>385.82098288079243</v>
+        <v>270.67248177265901</v>
       </c>
       <c r="I102">
-        <v>177.82713291420779</v>
+        <v>177.82713291420799</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -4088,28 +4107,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C103" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D103">
-        <v>450.02077272727269</v>
+        <v>450.02</v>
       </c>
       <c r="E103">
-        <v>486.14431818181822</v>
+        <v>486.14</v>
       </c>
       <c r="F103">
-        <v>3.0327046793822112</v>
+        <v>3.0327000000000002</v>
       </c>
       <c r="G103">
         <v>14.86</v>
       </c>
       <c r="H103">
-        <v>397.39561236721619</v>
+        <v>278.79265622583802</v>
       </c>
       <c r="I103">
-        <v>168.67487505697758</v>
+        <v>168.67487505697801</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -4117,28 +4136,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C104" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D104">
-        <v>434.20171428571427</v>
+        <v>434.2</v>
       </c>
       <c r="E104">
-        <v>463.93228571428568</v>
+        <v>463.93</v>
       </c>
       <c r="F104">
-        <v>2.7200177442321261</v>
+        <v>2.72</v>
       </c>
       <c r="G104">
         <v>14.26</v>
       </c>
       <c r="H104">
-        <v>410.90706318770162</v>
+        <v>288.27160653751702</v>
       </c>
       <c r="I104">
-        <v>156.54189054726777</v>
+        <v>156.541890547268</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -4146,28 +4165,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D105">
-        <v>545.88223809523811</v>
+        <v>545.88</v>
       </c>
       <c r="E105">
-        <v>464.84533333333337</v>
+        <v>464.85</v>
       </c>
       <c r="F105">
-        <v>2.6223954581408582</v>
+        <v>2.6223999999999998</v>
       </c>
       <c r="G105">
         <v>14.11</v>
       </c>
       <c r="H105">
-        <v>428.16515984158508</v>
+        <v>300.37901401209302</v>
       </c>
       <c r="I105">
-        <v>148.65185865607646</v>
+        <v>148.651858656076</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -4175,28 +4194,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C106" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D106">
-        <v>500.09918181818188</v>
+        <v>500.1</v>
       </c>
       <c r="E106">
-        <v>458.96622727272728</v>
+        <v>458.97</v>
       </c>
       <c r="F106">
-        <v>2.6133196292609329</v>
+        <v>2.6133000000000002</v>
       </c>
       <c r="G106">
         <v>14.65</v>
       </c>
       <c r="H106">
-        <v>441.43827979667418</v>
+        <v>309.690763446468</v>
       </c>
       <c r="I106">
-        <v>149.70016857375441</v>
+        <v>149.70016857375401</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -4204,28 +4223,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C107" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D107">
-        <v>488.44639999999998</v>
+        <v>488.45</v>
       </c>
       <c r="E107">
-        <v>417.96120000000002</v>
+        <v>417.96</v>
       </c>
       <c r="F107">
-        <v>2.7070669134093142</v>
+        <v>2.7071000000000001</v>
       </c>
       <c r="G107">
         <v>15.07</v>
       </c>
       <c r="H107">
-        <v>450.26704539260771</v>
+        <v>315.88457871539703</v>
       </c>
       <c r="I107">
-        <v>150.97246472639222</v>
+        <v>150.97246472639199</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -4233,28 +4252,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C108" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D108">
-        <v>461.44873913043477</v>
+        <v>461.45</v>
       </c>
       <c r="E108">
-        <v>394.7829565217391</v>
+        <v>394.78</v>
       </c>
       <c r="F108">
-        <v>2.5213324857901411</v>
+        <v>2.5213000000000001</v>
       </c>
       <c r="G108">
         <v>15.01</v>
       </c>
       <c r="H108">
-        <v>451.1675794833929</v>
+        <v>316.51634787282802</v>
       </c>
       <c r="I108">
-        <v>150.07123745496048</v>
+        <v>150.07123745496</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -4262,28 +4281,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D109">
-        <v>447.99085714285718</v>
+        <v>447.99</v>
       </c>
       <c r="E109">
-        <v>389.07528571428571</v>
+        <v>389.08</v>
       </c>
       <c r="F109">
-        <v>2.5298220307517871</v>
+        <v>2.5297999999999998</v>
       </c>
       <c r="G109">
         <v>15.31</v>
       </c>
       <c r="H109">
-        <v>456.13042285771019</v>
+        <v>319.99802769942897</v>
       </c>
       <c r="I109">
-        <v>151.40520532868925</v>
+        <v>151.40520532868899</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -4291,28 +4310,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C110" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D110">
-        <v>449.49545000000001</v>
+        <v>449.5</v>
       </c>
       <c r="E110">
-        <v>381.36264999999997</v>
+        <v>381.36</v>
       </c>
       <c r="F110">
-        <v>2.6324296004542131</v>
+        <v>2.6324000000000001</v>
       </c>
       <c r="G110">
         <v>15.16</v>
       </c>
       <c r="H110">
-        <v>467.07755300629532</v>
+        <v>327.67798036421499</v>
       </c>
       <c r="I110">
-        <v>146.40801768547217</v>
+        <v>146.408017685472</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -4320,28 +4339,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D111">
-        <v>478.74829999999997</v>
+        <v>478.75</v>
       </c>
       <c r="E111">
-        <v>414.35449999999997</v>
+        <v>414.35</v>
       </c>
       <c r="F111">
-        <v>2.5160641675586191</v>
+        <v>2.5160999999999998</v>
       </c>
       <c r="G111">
         <v>15.75</v>
       </c>
       <c r="H111">
-        <v>474.55079385439598</v>
+        <v>332.92082805004202</v>
       </c>
       <c r="I111">
-        <v>149.7105856783669</v>
+        <v>149.71058567836701</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -4349,28 +4368,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D112">
-        <v>494.1304761904762</v>
+        <v>494.13</v>
       </c>
       <c r="E112">
-        <v>405.96990476190479</v>
+        <v>405.97</v>
       </c>
       <c r="F112">
-        <v>2.4937647146979089</v>
+        <v>2.4937999999999998</v>
       </c>
       <c r="G112">
         <v>16.47</v>
       </c>
       <c r="H112">
-        <v>480.24540338064878</v>
+        <v>336.91587798664301</v>
       </c>
       <c r="I112">
-        <v>154.69812071790591</v>
+        <v>154.69812071790599</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -4378,28 +4397,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C113" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D113">
-        <v>467.35950000000003</v>
+        <v>467.36</v>
       </c>
       <c r="E113">
-        <v>388.99759999999998</v>
+        <v>389</v>
       </c>
       <c r="F113">
-        <v>2.4611481334244338</v>
+        <v>2.4611000000000001</v>
       </c>
       <c r="G113">
         <v>16.239999999999998</v>
       </c>
       <c r="H113">
-        <v>486.48859362459717</v>
+        <v>341.29578440046902</v>
       </c>
       <c r="I113">
-        <v>150.58025153626966</v>
+        <v>150.58025153627</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -4407,28 +4426,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C114" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D114">
-        <v>453.95531578947367</v>
+        <v>453.96</v>
       </c>
       <c r="E114">
-        <v>374.65157894736842</v>
+        <v>374.65</v>
       </c>
       <c r="F114">
-        <v>2.349897228751884</v>
+        <v>2.3498999999999999</v>
       </c>
       <c r="G114">
         <v>15.88</v>
       </c>
       <c r="H114">
-        <v>498.65080846521198</v>
+        <v>349.82817901048099</v>
       </c>
       <c r="I114">
-        <v>143.65099089246442</v>
+        <v>143.65099089246399</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -4436,28 +4455,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D115">
-        <v>444.09773913043477</v>
+        <v>444.1</v>
       </c>
       <c r="E115">
-        <v>365.77652173913049</v>
+        <v>365.78</v>
       </c>
       <c r="F115">
-        <v>2.316832641609115</v>
+        <v>2.3168000000000002</v>
       </c>
       <c r="G115">
         <v>15.58</v>
       </c>
       <c r="H115">
-        <v>510.61842786837718</v>
+        <v>358.22405530673302</v>
       </c>
       <c r="I115">
-        <v>137.63396605551128</v>
+        <v>137.633966055511</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -4465,25 +4484,25 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C116" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D116">
-        <v>422.41115789473679</v>
+        <v>422.41</v>
       </c>
       <c r="E116">
-        <v>369.43226315789468</v>
+        <v>369.43</v>
       </c>
       <c r="F116">
-        <v>2.6113299353267458</v>
+        <v>2.6113</v>
       </c>
       <c r="G116">
         <v>15.59</v>
       </c>
       <c r="H116">
-        <v>523.89450699295492</v>
+        <v>367.53788074470799</v>
       </c>
       <c r="I116">
         <v>134.23226726456301</v>
@@ -4494,28 +4513,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C117" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D117">
-        <v>403.12809090909087</v>
+        <v>403.13</v>
       </c>
       <c r="E117">
-        <v>360.29881818181821</v>
+        <v>360.3</v>
       </c>
       <c r="F117">
-        <v>2.5168990049223172</v>
+        <v>2.5169000000000001</v>
       </c>
       <c r="G117">
         <v>15.99</v>
       </c>
       <c r="H117">
-        <v>530.70513558386324</v>
+        <v>372.31587319438898</v>
       </c>
       <c r="I117">
-        <v>135.90950444480652</v>
+        <v>135.909504444807</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -4523,28 +4542,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C118" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D118">
-        <v>410.01390909090912</v>
+        <v>410.01</v>
       </c>
       <c r="E118">
-        <v>367.06768181818182</v>
+        <v>367.07</v>
       </c>
       <c r="F118">
-        <v>2.277803797344701</v>
+        <v>2.2778</v>
       </c>
       <c r="G118">
         <v>16.440000000000001</v>
       </c>
       <c r="H118">
-        <v>537.07359721086971</v>
+        <v>376.78366367272201</v>
       </c>
       <c r="I118">
-        <v>138.07742073681297</v>
+        <v>138.077420736813</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -4552,28 +4571,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D119">
-        <v>436.16489999999999</v>
+        <v>436.16</v>
       </c>
       <c r="E119">
-        <v>369.02480000000003</v>
+        <v>369.02</v>
       </c>
       <c r="F119">
-        <v>2.235447625020651</v>
+        <v>2.2353999999999998</v>
       </c>
       <c r="G119">
         <v>17.649999999999999</v>
       </c>
       <c r="H119">
-        <v>546.20384836345443</v>
+        <v>383.18898595515799</v>
       </c>
       <c r="I119">
-        <v>145.7620976253298</v>
+        <v>145.76209762533</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -4581,28 +4600,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C120" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D120">
-        <v>428.42117391304339</v>
+        <v>428.42</v>
       </c>
       <c r="E120">
-        <v>367.15060869565218</v>
+        <v>367.15</v>
       </c>
       <c r="F120">
-        <v>2.5317971156960009</v>
+        <v>2.5318000000000001</v>
       </c>
       <c r="G120">
         <v>17.829999999999998</v>
       </c>
       <c r="H120">
-        <v>553.85070224054277</v>
+        <v>388.55363175853</v>
       </c>
       <c r="I120">
-        <v>145.21560479963961</v>
+        <v>145.21560479964</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -4610,28 +4629,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C121" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D121">
-        <v>388.48874999999998</v>
+        <v>388.49</v>
       </c>
       <c r="E121">
-        <v>349.24675000000002</v>
+        <v>349.25</v>
       </c>
       <c r="F121">
-        <v>2.855032825637148</v>
+        <v>2.855</v>
       </c>
       <c r="G121">
         <v>17.510000000000002</v>
       </c>
       <c r="H121">
-        <v>564.373865583113</v>
+        <v>395.93615076194197</v>
       </c>
       <c r="I121">
-        <v>139.95032355199007</v>
+        <v>139.95032355199001</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -4639,28 +4658,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C122" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D122">
-        <v>362.29509523809531</v>
+        <v>362.3</v>
       </c>
       <c r="E122">
-        <v>338.04423809523809</v>
+        <v>338.04</v>
       </c>
       <c r="F122">
-        <v>2.8276212077622591</v>
+        <v>2.8275999999999999</v>
       </c>
       <c r="G122">
         <v>17.7</v>
       </c>
       <c r="H122">
-        <v>572.83947356685962</v>
+        <v>401.87519302337103</v>
       </c>
       <c r="I122">
-        <v>139.37824279835723</v>
+        <v>139.37824279835701</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -4668,25 +4687,25 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D123">
-        <v>370.35747619047618</v>
+        <v>370.36</v>
       </c>
       <c r="E123">
-        <v>347.97366666666659</v>
+        <v>347.97</v>
       </c>
       <c r="F123">
-        <v>2.966698143781433</v>
+        <v>2.9666999999999999</v>
       </c>
       <c r="G123">
         <v>17.559999999999999</v>
       </c>
       <c r="H123">
-        <v>580.8592261967957</v>
+        <v>407.50144572569798</v>
       </c>
       <c r="I123">
         <v>136.36668246465601</v>
@@ -4697,28 +4716,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D124">
-        <v>356.24894999999998</v>
+        <v>356.25</v>
       </c>
       <c r="E124">
-        <v>344.51530000000002</v>
+        <v>344.52</v>
       </c>
       <c r="F124">
-        <v>2.3634553690012252</v>
+        <v>2.3635000000000002</v>
       </c>
       <c r="G124">
         <v>18.88</v>
       </c>
       <c r="H124">
-        <v>598.86586220889637</v>
+        <v>420.13399054319501</v>
       </c>
       <c r="I124">
-        <v>142.20900186102716</v>
+        <v>142.20900186102699</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -4726,28 +4745,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C125" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D125">
-        <v>364.62880952380948</v>
+        <v>364.63</v>
       </c>
       <c r="E125">
-        <v>332.57342857142862</v>
+        <v>332.57</v>
       </c>
       <c r="F125">
-        <v>2.278398041910763</v>
+        <v>2.2784</v>
       </c>
       <c r="G125">
         <v>19.55</v>
       </c>
       <c r="H125">
-        <v>609.64544772865645</v>
+        <v>427.69640237297199</v>
       </c>
       <c r="I125">
-        <v>144.6518798482756</v>
+        <v>144.651879848276</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -4755,28 +4774,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C126" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D126">
-        <v>400.64357894736838</v>
+        <v>400.64</v>
       </c>
       <c r="E126">
-        <v>347.43084210526308</v>
+        <v>347.43</v>
       </c>
       <c r="F126">
-        <v>2.320105810656333</v>
+        <v>2.3201000000000001</v>
       </c>
       <c r="G126">
         <v>19.95</v>
       </c>
       <c r="H126">
-        <v>624.27693847414434</v>
+        <v>437.96111602992403</v>
       </c>
       <c r="I126">
-        <v>144.15186435887037</v>
+        <v>144.15186435887</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -4784,28 +4803,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D127">
-        <v>412.09071428571428</v>
+        <v>412.09</v>
       </c>
       <c r="E127">
-        <v>354.31638095238088</v>
+        <v>354.32</v>
       </c>
       <c r="F127">
-        <v>2.3215668815518389</v>
+        <v>2.3216000000000001</v>
       </c>
       <c r="G127">
         <v>20.36</v>
       </c>
       <c r="H127">
-        <v>638.63530805904952</v>
+        <v>448.03422169861199</v>
       </c>
       <c r="I127">
-        <v>143.80682685925964</v>
+        <v>143.80682685926001</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -4813,28 +4832,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C128" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D128">
-        <v>408.55271428571427</v>
+        <v>408.55</v>
       </c>
       <c r="E128">
-        <v>355.97042857142861</v>
+        <v>355.97</v>
       </c>
       <c r="F128">
-        <v>2.065269766898731</v>
+        <v>2.0653000000000001</v>
       </c>
       <c r="G128">
         <v>20.6</v>
       </c>
       <c r="H128">
-        <v>655.87846137664383</v>
+        <v>460.13114568447401</v>
       </c>
       <c r="I128">
-        <v>141.67672418859502</v>
+        <v>141.67672418859499</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -4842,28 +4861,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D129">
-        <v>469.48277272727267</v>
+        <v>469.48</v>
       </c>
       <c r="E129">
-        <v>387.74472727272729</v>
+        <v>387.74</v>
       </c>
       <c r="F129">
-        <v>1.937971326949482</v>
+        <v>1.9379999999999999</v>
       </c>
       <c r="G129">
         <v>25.17</v>
       </c>
       <c r="H129">
-        <v>669.65190906555324</v>
+        <v>469.79389974384799</v>
       </c>
       <c r="I129">
-        <v>169.5464729908303</v>
+        <v>169.54647299083001</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -4871,28 +4890,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D130">
-        <v>529.12957142857135</v>
+        <v>529.13</v>
       </c>
       <c r="E130">
-        <v>407.98590476190469</v>
+        <v>407.99</v>
       </c>
       <c r="F130">
-        <v>2.042160419513714</v>
+        <v>2.0421999999999998</v>
       </c>
       <c r="G130">
         <v>28.4</v>
       </c>
       <c r="H130">
-        <v>694.42902970097862</v>
+        <v>487.17627403437098</v>
       </c>
       <c r="I130">
-        <v>184.47823203142755</v>
+        <v>184.47823203142801</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -4900,28 +4919,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D131">
-        <v>571.3922380952381</v>
+        <v>571.39</v>
       </c>
       <c r="E131">
-        <v>391.02323809523813</v>
+        <v>391.02</v>
       </c>
       <c r="F131">
-        <v>2.01412257067296</v>
+        <v>2.0141</v>
       </c>
       <c r="G131">
         <v>27.45</v>
       </c>
       <c r="H131">
-        <v>715.95632962170896</v>
+        <v>502.278738529436</v>
       </c>
       <c r="I131">
-        <v>172.94597987946497</v>
+        <v>172.945979879465</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -4929,28 +4948,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D132">
-        <v>668.49626086956528</v>
+        <v>668.5</v>
       </c>
       <c r="E132">
-        <v>407.3036086956522</v>
+        <v>407.3</v>
       </c>
       <c r="F132">
-        <v>1.944359299128771</v>
+        <v>1.9443999999999999</v>
       </c>
       <c r="G132">
         <v>36</v>
       </c>
       <c r="H132">
-        <v>743.87862647695556</v>
+        <v>521.86760933208404</v>
       </c>
       <c r="I132">
-        <v>218.30067357259031</v>
+        <v>218.30067357259</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -4958,28 +4977,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C133" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D133">
-        <v>667.49126315789476</v>
+        <v>667.49</v>
       </c>
       <c r="E133">
-        <v>408.76078947368421</v>
+        <v>408.76</v>
       </c>
       <c r="F133">
-        <v>1.749469585451281</v>
+        <v>1.7495000000000001</v>
       </c>
       <c r="G133">
         <v>39.299999999999997</v>
       </c>
       <c r="H133">
-        <v>792.23073719795764</v>
+        <v>555.78900393867002</v>
       </c>
       <c r="I133">
-        <v>223.76673112683358</v>
+        <v>223.766731126834</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -4987,28 +5006,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C134" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D134">
-        <v>658.14854545454546</v>
+        <v>658.15</v>
       </c>
       <c r="E134">
-        <v>405.5604090909091</v>
+        <v>405.56</v>
       </c>
       <c r="F134">
-        <v>1.763051851148622</v>
+        <v>1.7630999999999999</v>
       </c>
       <c r="G134">
         <v>34.5</v>
       </c>
       <c r="H134">
-        <v>835.01119700664731</v>
+        <v>585.80161015135798</v>
       </c>
       <c r="I134">
-        <v>186.37233714954198</v>
+        <v>186.37233714954201</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -5016,28 +5035,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C135" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D135">
-        <v>655.79755</v>
+        <v>655.8</v>
       </c>
       <c r="E135">
-        <v>433.86349999999999</v>
+        <v>433.86</v>
       </c>
       <c r="F135">
-        <v>1.7673766864168541</v>
+        <v>1.7674000000000001</v>
       </c>
       <c r="G135">
         <v>36</v>
       </c>
       <c r="H135">
-        <v>861.73155531086024</v>
+        <v>604.54726167620095</v>
       </c>
       <c r="I135">
-        <v>188.44523473158949</v>
+        <v>188.44523473159001</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -5045,16 +5064,16 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C136" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D136">
-        <v>773.56721052631576</v>
+        <v>773.57</v>
       </c>
       <c r="E136">
-        <v>451.96263157894731</v>
+        <v>451.96</v>
       </c>
       <c r="F136">
         <v>1.92</v>
@@ -5063,10 +5082,10 @@
         <v>38.5</v>
       </c>
       <c r="H136">
-        <v>884.13657574894251</v>
+        <v>620.26549047978199</v>
       </c>
       <c r="I136">
-        <v>196.42466799778521</v>
+        <v>196.42466799778501</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -5074,16 +5093,16 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D137">
-        <v>700.99833333333333</v>
+        <v>701</v>
       </c>
       <c r="E137">
-        <v>428.57780952380949</v>
+        <v>428.58</v>
       </c>
       <c r="F137">
         <v>1.63</v>
@@ -5092,10 +5111,10 @@
         <v>35.5</v>
       </c>
       <c r="H137">
-        <v>909.77653644566169</v>
+        <v>638.25318970369597</v>
       </c>
       <c r="I137">
-        <v>176.01443120723374</v>
+        <v>176.014431207234</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -5103,16 +5122,16 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C138" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D138">
-        <v>679.29663157894743</v>
+        <v>679.3</v>
       </c>
       <c r="E138">
-        <v>400.71994736842112</v>
+        <v>400.72</v>
       </c>
       <c r="F138">
         <v>1.79</v>
@@ -5121,10 +5140,10 @@
         <v>38.799999999999997</v>
       </c>
       <c r="H138">
-        <v>944.3480448305969</v>
+        <v>662.50681091243598</v>
       </c>
       <c r="I138">
-        <v>185.33365710984472</v>
+        <v>185.33365710984501</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -5132,16 +5151,16 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C139" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D139">
-        <v>748.3870952380953</v>
+        <v>748.39</v>
       </c>
       <c r="E139">
-        <v>396.34938095238101</v>
+        <v>396.35</v>
       </c>
       <c r="F139">
         <v>1.6</v>
@@ -5150,10 +5169,10 @@
         <v>42.65</v>
       </c>
       <c r="H139">
-        <v>988.73240293763502</v>
+        <v>693.64463102532102</v>
       </c>
       <c r="I139">
-        <v>194.57853257059639</v>
+        <v>194.578532570596</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -5161,28 +5180,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D140">
-        <v>838.95128571428563</v>
+        <v>838.95</v>
       </c>
       <c r="E140">
-        <v>390.72923809523809</v>
+        <v>390.73</v>
       </c>
       <c r="F140">
-        <v>1.529328552142305</v>
+        <v>1.5293000000000001</v>
       </c>
       <c r="G140">
         <v>45</v>
       </c>
       <c r="H140">
-        <v>1022.349304637515</v>
+        <v>717.22854848018198</v>
       </c>
       <c r="I140">
-        <v>198.54907280656587</v>
+        <v>198.54907280656599</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -5190,28 +5209,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C141" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D141">
-        <v>924.9255454545455</v>
+        <v>924.93</v>
       </c>
       <c r="E141">
-        <v>408.17250000000001</v>
+        <v>408.17</v>
       </c>
       <c r="F141">
-        <v>1.614401720242761</v>
+        <v>1.6144000000000001</v>
       </c>
       <c r="G141">
         <v>44.5</v>
       </c>
       <c r="H141">
-        <v>1054.0421330812769</v>
+        <v>739.46263348306695</v>
       </c>
       <c r="I141">
-        <v>190.43935208303014</v>
+        <v>190.43935208303</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -5219,28 +5238,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C142" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D142">
-        <v>882.76019999999994</v>
+        <v>882.76</v>
       </c>
       <c r="E142">
-        <v>409.87990000000002</v>
+        <v>409.88</v>
       </c>
       <c r="F142">
-        <v>1.8565122668361571</v>
+        <v>1.8565</v>
       </c>
       <c r="G142">
         <v>42.3</v>
       </c>
       <c r="H142">
-        <v>1082.5012706744719</v>
+        <v>759.42812458711001</v>
       </c>
       <c r="I142">
-        <v>176.26521215085228</v>
+        <v>176.26521215085199</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -5248,28 +5267,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C143" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D143">
-        <v>789.66881818181821</v>
+        <v>789.67</v>
       </c>
       <c r="E143">
         <v>399.8</v>
       </c>
       <c r="F143">
-        <v>1.9696876465696129</v>
+        <v>1.9697</v>
       </c>
       <c r="G143">
         <v>43.7</v>
       </c>
       <c r="H143">
-        <v>1106.31629862931</v>
+        <v>776.13554332802698</v>
       </c>
       <c r="I143">
-        <v>178.17910857106415</v>
+        <v>178.17910857106401</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -5277,28 +5296,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C144" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D144">
-        <v>1568.443181818182</v>
+        <v>1568.44</v>
       </c>
       <c r="E144">
-        <v>422.31918181818179</v>
+        <v>422.32</v>
       </c>
       <c r="F144">
-        <v>2.2014392162288621</v>
+        <v>2.2014</v>
       </c>
       <c r="G144">
         <v>60</v>
       </c>
       <c r="H144">
-        <v>1150.5689505744831</v>
+        <v>807.18096506114796</v>
       </c>
       <c r="I144">
-        <v>235.23029647649727</v>
+        <v>235.23029647649699</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -5306,16 +5325,16 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C145" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D145">
-        <v>2169.6253999999999</v>
+        <v>2169.63</v>
       </c>
       <c r="E145">
-        <v>401.57265000000001</v>
+        <v>401.57</v>
       </c>
       <c r="F145">
         <v>1.91</v>
@@ -5324,10 +5343,10 @@
         <v>58.25</v>
       </c>
       <c r="H145">
-        <v>1218.4525186583769</v>
+        <v>854.80464199975495</v>
       </c>
       <c r="I145">
-        <v>215.64628218061011</v>
+        <v>215.64628218061</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -5335,28 +5354,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C146" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D146">
-        <v>2107.811454545455</v>
+        <v>2107.81</v>
       </c>
       <c r="E146">
-        <v>389.02831818181818</v>
+        <v>389.03</v>
       </c>
       <c r="F146">
-        <v>2.0090217288104459</v>
+        <v>2.0089999999999999</v>
       </c>
       <c r="G146">
         <v>66</v>
       </c>
       <c r="H146">
-        <v>1258.6614517741029</v>
+        <v>883.01319518574701</v>
       </c>
       <c r="I146">
-        <v>236.53186683097721</v>
+        <v>236.53186683097701</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -5364,28 +5383,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C147" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D147">
-        <v>2336.2613684210528</v>
+        <v>2336.2600000000002</v>
       </c>
       <c r="E147">
-        <v>373.08278947368422</v>
+        <v>373.08</v>
       </c>
       <c r="F147">
-        <v>1.9765187878822299</v>
+        <v>1.9764999999999999</v>
       </c>
       <c r="G147">
         <v>66.25</v>
       </c>
       <c r="H147">
-        <v>1312.78389420039</v>
+        <v>920.98276257873397</v>
       </c>
       <c r="I147">
-        <v>227.63932969511382</v>
+        <v>227.63932969511399</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -5393,28 +5412,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C148" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D148">
-        <v>2045.411095238095</v>
+        <v>2045.41</v>
       </c>
       <c r="E148">
-        <v>330.12709523809531</v>
+        <v>330.13</v>
       </c>
       <c r="F148">
-        <v>1.9672101478832269</v>
+        <v>1.9672000000000001</v>
       </c>
       <c r="G148">
         <v>73.5</v>
       </c>
       <c r="H148">
-        <v>1361.3568982858039</v>
+        <v>955.05912479414701</v>
       </c>
       <c r="I148">
-        <v>243.53982980791272</v>
+        <v>243.53982980791301</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -5422,28 +5441,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C149" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D149">
-        <v>1932.3799523809521</v>
+        <v>1932.38</v>
       </c>
       <c r="E149">
-        <v>319.96052380952381</v>
+        <v>319.95999999999998</v>
       </c>
       <c r="F149">
-        <v>2.3233532020716789</v>
+        <v>2.3233999999999999</v>
       </c>
       <c r="G149">
         <v>74</v>
       </c>
       <c r="H149">
-        <v>1392.668106946378</v>
+        <v>977.02548466441306</v>
       </c>
       <c r="I149">
-        <v>239.68383513589541</v>
+        <v>239.68383513589501</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -5451,28 +5470,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C150" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D150">
-        <v>2017.343315789474</v>
+        <v>2017.34</v>
       </c>
       <c r="E150">
-        <v>336.31394736842111</v>
+        <v>336.31</v>
       </c>
       <c r="F150">
-        <v>2.2702413109641908</v>
+        <v>2.2702</v>
       </c>
       <c r="G150">
         <v>74.5</v>
       </c>
       <c r="H150">
-        <v>1420.5214690853049</v>
+        <v>996.56599435770102</v>
       </c>
       <c r="I150">
-        <v>236.57188285140708</v>
+        <v>236.571882851407</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -5480,28 +5499,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C151" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D151">
-        <v>3375.8178636363641</v>
+        <v>3375.82</v>
       </c>
       <c r="E151">
-        <v>578.17372727272732</v>
+        <v>578.16999999999996</v>
       </c>
       <c r="F151">
-        <v>2.2180591964140368</v>
+        <v>2.2181000000000002</v>
       </c>
       <c r="G151">
         <v>78.5</v>
       </c>
       <c r="H151">
-        <v>1467.3986775651199</v>
+        <v>1029.4526721715099</v>
       </c>
       <c r="I151">
-        <v>241.31048297245218</v>
+        <v>241.31048297245201</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -5509,28 +5528,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D152">
-        <v>3803.0427142857138</v>
+        <v>3803.04</v>
       </c>
       <c r="E152">
-        <v>675.98014285714294</v>
+        <v>675.98</v>
       </c>
       <c r="F152">
-        <v>3.2868810915916038</v>
+        <v>3.2869000000000002</v>
       </c>
       <c r="G152">
         <v>108</v>
       </c>
       <c r="H152">
-        <v>1489.409657728597</v>
+        <v>1044.8944622540801</v>
       </c>
       <c r="I152">
-        <v>327.08772440180525</v>
+        <v>327.08772440180502</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5538,28 +5557,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C153" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D153">
-        <v>3003.4011999999998</v>
+        <v>3003.4</v>
       </c>
       <c r="E153">
-        <v>600.97929999999997</v>
+        <v>600.98</v>
       </c>
       <c r="F153">
-        <v>3.0017462475974859</v>
+        <v>3.0017</v>
       </c>
       <c r="G153">
         <v>115</v>
       </c>
       <c r="H153">
-        <v>1511.750802594526</v>
+        <v>1060.56787918789</v>
       </c>
       <c r="I153">
-        <v>343.14074353409603</v>
+        <v>343.14074353409598</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -5567,28 +5586,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C154" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D154">
-        <v>2538.5572727272729</v>
+        <v>2538.56</v>
       </c>
       <c r="E154">
-        <v>516.2921818181818</v>
+        <v>516.29</v>
       </c>
       <c r="F154">
-        <v>2.7702254972161731</v>
+        <v>2.7702</v>
       </c>
       <c r="G154">
         <v>116</v>
       </c>
       <c r="H154">
-        <v>1545.009320251605</v>
+        <v>1083.9003725300199</v>
       </c>
       <c r="I154">
-        <v>338.67375350936049</v>
+        <v>338.67375350936101</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -5596,28 +5615,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C155" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D155">
-        <v>2322.4097727272729</v>
+        <v>2322.41</v>
       </c>
       <c r="E155">
-        <v>484.5533636363636</v>
+        <v>484.55</v>
       </c>
       <c r="F155">
-        <v>2.5295964691761812</v>
+        <v>2.5295999999999998</v>
       </c>
       <c r="G155">
         <v>131</v>
       </c>
       <c r="H155">
-        <v>1574.3644973363851</v>
+        <v>1104.4944796080899</v>
       </c>
       <c r="I155">
-        <v>375.33638209981245</v>
+        <v>375.336382099812</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -5625,28 +5644,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C156" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D156">
-        <v>2119.03680952381</v>
+        <v>2119.04</v>
       </c>
       <c r="E156">
-        <v>445.89404761904763</v>
+        <v>445.89</v>
       </c>
       <c r="F156">
-        <v>2.3778576940878779</v>
+        <v>2.3778999999999999</v>
       </c>
       <c r="G156">
         <v>131</v>
       </c>
       <c r="H156">
-        <v>1616.872338764467</v>
+        <v>1134.31583055751</v>
       </c>
       <c r="I156">
-        <v>365.46872648472487</v>
+        <v>365.46872648472498</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -5654,28 +5673,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C157" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D157">
-        <v>1504.97780952381</v>
+        <v>1504.98</v>
       </c>
       <c r="E157">
-        <v>424.23652380952382</v>
+        <v>424.24</v>
       </c>
       <c r="F157">
-        <v>2.2659687054496391</v>
+        <v>2.266</v>
       </c>
       <c r="G157">
         <v>140</v>
       </c>
       <c r="H157">
-        <v>1662.1447642498731</v>
+        <v>1166.0766738131199</v>
       </c>
       <c r="I157">
-        <v>379.93897368240027</v>
+        <v>379.93897368239999</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -5683,28 +5702,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C158" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D158">
-        <v>1409.3947142857139</v>
+        <v>1409.39</v>
       </c>
       <c r="E158">
-        <v>415.16385714285718</v>
+        <v>415.16</v>
       </c>
       <c r="F158">
-        <v>1.992343621116379</v>
+        <v>1.9923</v>
       </c>
       <c r="G158">
         <v>163</v>
       </c>
       <c r="H158">
-        <v>1725.3062652913679</v>
+        <v>1210.3875874180201</v>
       </c>
       <c r="I158">
-        <v>426.16331344777905</v>
+        <v>426.16331344777899</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -5712,28 +5731,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C159" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D159">
-        <v>1378.1137894736839</v>
+        <v>1378.11</v>
       </c>
       <c r="E159">
-        <v>391.53357894736843</v>
+        <v>391.53</v>
       </c>
       <c r="F159">
-        <v>2.019343321400906</v>
+        <v>2.0192999999999999</v>
       </c>
       <c r="G159">
         <v>149</v>
       </c>
       <c r="H159">
-        <v>1780.5160657806921</v>
+        <v>1249.1199902154001</v>
       </c>
       <c r="I159">
-        <v>377.48093940956318</v>
+        <v>377.48093940956301</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -5741,28 +5760,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C160" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D160">
-        <v>1391.6025</v>
+        <v>1391.6</v>
       </c>
       <c r="E160">
-        <v>369.65427272727271</v>
+        <v>369.65</v>
       </c>
       <c r="F160">
-        <v>1.8538681869858751</v>
+        <v>1.8539000000000001</v>
       </c>
       <c r="G160">
         <v>160</v>
       </c>
       <c r="H160">
-        <v>1851.7367084119189</v>
+        <v>1299.0847898240099</v>
       </c>
       <c r="I160">
-        <v>389.75832670063306</v>
+        <v>389.75832670063301</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -5770,28 +5789,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C161" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D161">
-        <v>1422.1256315789469</v>
+        <v>1422.13</v>
       </c>
       <c r="E161">
-        <v>366.04305263157897</v>
+        <v>366.04</v>
       </c>
       <c r="F161">
-        <v>1.8751297166824099</v>
+        <v>1.8751</v>
       </c>
       <c r="G161">
         <v>148</v>
       </c>
       <c r="H161">
-        <v>1925.806176748396</v>
+        <v>1351.04818141697</v>
       </c>
       <c r="I161">
-        <v>346.6600501904669</v>
+        <v>346.66005019046702</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -5799,25 +5818,25 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C162" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D162">
-        <v>1471.5959473684211</v>
+        <v>1471.6</v>
       </c>
       <c r="E162">
-        <v>359.79510526315789</v>
+        <v>359.8</v>
       </c>
       <c r="F162">
-        <v>1.8165651902276121</v>
+        <v>1.8166</v>
       </c>
       <c r="G162">
         <v>141</v>
       </c>
       <c r="H162">
-        <v>1995.135199111339</v>
+        <v>1399.68591594798</v>
       </c>
       <c r="I162">
         <v>318.787612679066</v>
@@ -5828,28 +5847,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C163" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D163">
-        <v>1568.1148695652171</v>
+        <v>1568.11</v>
       </c>
       <c r="E163">
-        <v>370.90239130434787</v>
+        <v>370.9</v>
       </c>
       <c r="F163">
-        <v>1.7838564112823589</v>
+        <v>1.7839</v>
       </c>
       <c r="G163">
         <v>136</v>
       </c>
       <c r="H163">
-        <v>2090.9016886686832</v>
+        <v>1466.87083991349</v>
       </c>
       <c r="I163">
-        <v>293.39989256370103</v>
+        <v>293.39989256370097</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -5857,28 +5876,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C164" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D164">
-        <v>1584.149454545455</v>
+        <v>1584.15</v>
       </c>
       <c r="E164">
-        <v>349.5269090909091</v>
+        <v>349.53</v>
       </c>
       <c r="F164">
-        <v>1.7329975550833909</v>
+        <v>1.7330000000000001</v>
       </c>
       <c r="G164">
         <v>145</v>
       </c>
       <c r="H164">
-        <v>2176.6286579040989</v>
+        <v>1527.0125443499401</v>
       </c>
       <c r="I164">
-        <v>300.49573671905307</v>
+        <v>300.49573671905301</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,28 +5905,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C165" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D165">
-        <v>1547.9331500000001</v>
+        <v>1547.93</v>
       </c>
       <c r="E165">
-        <v>340.41559999999998</v>
+        <v>340.42</v>
       </c>
       <c r="F165">
-        <v>1.9320565050488541</v>
+        <v>1.9320999999999999</v>
       </c>
       <c r="G165">
         <v>152</v>
       </c>
       <c r="H165">
-        <v>2248.4574036149338</v>
+        <v>1577.40395831349</v>
       </c>
       <c r="I165">
-        <v>304.93942638646104</v>
+        <v>304.93942638646098</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -5915,28 +5934,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C166" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D166">
-        <v>1514.2534090909089</v>
+        <v>1514.25</v>
       </c>
       <c r="E166">
-        <v>342.87859090909092</v>
+        <v>342.88</v>
       </c>
       <c r="F166">
-        <v>1.703405468541608</v>
+        <v>1.7034</v>
       </c>
       <c r="G166">
         <v>163</v>
       </c>
       <c r="H166">
-        <v>2320.4080405306122</v>
+        <v>1627.88088497952</v>
       </c>
       <c r="I166">
-        <v>316.86764650265928</v>
+        <v>316.867646502659</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -5944,28 +5963,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C167" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D167">
-        <v>1596.6683809523811</v>
+        <v>1596.67</v>
       </c>
       <c r="E167">
-        <v>360.89814285714277</v>
+        <v>360.9</v>
       </c>
       <c r="F167">
-        <v>1.698241844452488</v>
+        <v>1.6981999999999999</v>
       </c>
       <c r="G167">
         <v>175.5</v>
       </c>
       <c r="H167">
-        <v>2390.0202817465311</v>
+        <v>1676.7173115289099</v>
       </c>
       <c r="I167">
-        <v>331.23040062670026</v>
+        <v>331.23040062669997</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -5973,28 +5992,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C168" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D168">
-        <v>1566.825636363636</v>
+        <v>1566.83</v>
       </c>
       <c r="E168">
-        <v>365.03109090909089</v>
+        <v>365.03</v>
       </c>
       <c r="F168">
-        <v>1.8522281373483429</v>
+        <v>1.8522000000000001</v>
       </c>
       <c r="G168">
         <v>176.5</v>
       </c>
       <c r="H168">
-        <v>2449.7707887901938</v>
+        <v>1718.6352443171299</v>
       </c>
       <c r="I168">
-        <v>324.9929300847063</v>
+        <v>324.99293008470602</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -6002,28 +6021,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C169" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D169">
-        <v>1543.6569999999999</v>
+        <v>1543.66</v>
       </c>
       <c r="E169">
-        <v>362.68261904761903</v>
+        <v>362.68</v>
       </c>
       <c r="F169">
-        <v>1.5793278069427279</v>
+        <v>1.5792999999999999</v>
       </c>
       <c r="G169">
         <v>182</v>
       </c>
       <c r="H169">
-        <v>2535.512766397851</v>
+        <v>1778.7874778682301</v>
       </c>
       <c r="I169">
-        <v>323.78762176741282</v>
+        <v>323.78762176741299</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -6031,28 +6050,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C170" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D170">
-        <v>1636.9419</v>
+        <v>1636.94</v>
       </c>
       <c r="E170">
-        <v>374.59535</v>
+        <v>374.6</v>
       </c>
       <c r="F170">
-        <v>1.524077204301922</v>
+        <v>1.5241</v>
       </c>
       <c r="G170">
         <v>193.5</v>
       </c>
       <c r="H170">
-        <v>2624.2557132217748</v>
+        <v>1841.04503959361</v>
       </c>
       <c r="I170">
-        <v>332.6055359770366</v>
+        <v>332.60553597703699</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -6060,28 +6079,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C171" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D171">
-        <v>1763.5622000000001</v>
+        <v>1763.56</v>
       </c>
       <c r="E171">
-        <v>381.69260000000003</v>
+        <v>381.69</v>
       </c>
       <c r="F171">
-        <v>1.4535844174951109</v>
+        <v>1.4536</v>
       </c>
       <c r="G171">
         <v>197.5</v>
       </c>
       <c r="H171">
-        <v>2689.8621060523192</v>
+        <v>1887.07116558345</v>
       </c>
       <c r="I171">
-        <v>331.20107571923978</v>
+        <v>331.20107571924001</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -6089,28 +6108,28 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C172" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D172">
-        <v>1728.903818181818</v>
+        <v>1728.9</v>
       </c>
       <c r="E172">
-        <v>385.84827272727267</v>
+        <v>385.85</v>
       </c>
       <c r="F172">
-        <v>1.422823400279098</v>
+        <v>1.4228000000000001</v>
       </c>
       <c r="G172">
         <v>204</v>
       </c>
       <c r="H172">
-        <v>2792.0768660823069</v>
+        <v>1958.7798698756301</v>
       </c>
       <c r="I172">
-        <v>329.57742224201809</v>
+        <v>329.57742224201797</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -6118,28 +6137,28 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C173" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D173">
-        <v>1838.0124499999999</v>
+        <v>1838.01</v>
       </c>
       <c r="E173">
-        <v>389.20895000000002</v>
+        <v>389.21</v>
       </c>
       <c r="F173">
-        <v>1.5438081716877301</v>
+        <v>1.5438000000000001</v>
       </c>
       <c r="G173">
         <v>209</v>
       </c>
       <c r="H173">
-        <v>2900.9678638595169</v>
+        <v>2035.1722848007801</v>
       </c>
       <c r="I173">
-        <v>324.98103969022713</v>
+        <v>324.98103969022702</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -6147,28 +6166,28 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C174" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D174">
-        <v>1764.3224210526321</v>
+        <v>1764.32</v>
       </c>
       <c r="E174">
-        <v>398.62936842105262</v>
+        <v>398.63</v>
       </c>
       <c r="F174">
-        <v>1.494020574046969</v>
+        <v>1.494</v>
       </c>
       <c r="G174">
         <v>207</v>
       </c>
       <c r="H174">
-        <v>3037.3133534609151</v>
+        <v>2130.82538218641</v>
       </c>
       <c r="I174">
-        <v>307.42232405129727</v>
+        <v>307.42232405129698</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -6176,25 +6195,25 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C175" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D175">
-        <v>1819.187391304348</v>
+        <v>1819.19</v>
       </c>
       <c r="E175">
-        <v>412.50708695652168</v>
+        <v>412.51</v>
       </c>
       <c r="F175">
-        <v>1.507731000735945</v>
+        <v>1.5077</v>
       </c>
       <c r="G175">
         <v>196</v>
       </c>
       <c r="H175">
-        <v>3240.8133481427958</v>
+        <v>2273.5906827929002</v>
       </c>
       <c r="I175">
         <v>272.80775262284101</v>
@@ -6205,28 +6224,28 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C176" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D176">
-        <v>1728.3041499999999</v>
+        <v>1728.3</v>
       </c>
       <c r="E176">
-        <v>393.00995</v>
+        <v>393.01</v>
       </c>
       <c r="F176">
-        <v>1.4360732129586149</v>
+        <v>1.4360999999999999</v>
       </c>
       <c r="G176">
         <v>196.5</v>
       </c>
       <c r="H176">
-        <v>3435.2621490313641</v>
+        <v>2410.00612376048</v>
       </c>
       <c r="I176">
-        <v>258.02234978045942</v>
+        <v>258.02234978045902</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -6234,28 +6253,28 @@
         <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C177" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D177">
-        <v>1881.7831904761899</v>
+        <v>1881.78</v>
       </c>
       <c r="E177">
-        <v>434.68528571428573</v>
+        <v>434.69</v>
       </c>
       <c r="F177">
-        <v>1.3032361554953471</v>
+        <v>1.3031999999999999</v>
       </c>
       <c r="G177">
         <v>201</v>
       </c>
       <c r="H177">
-        <v>3610.4605186319632</v>
+        <v>2532.9164360722598</v>
       </c>
       <c r="I177">
-        <v>251.12393772983611</v>
+        <v>251.123937729836</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -6263,28 +6282,28 @@
         <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C178" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D178">
-        <v>2150.381571428572</v>
+        <v>2150.38</v>
       </c>
       <c r="E178">
-        <v>457.26295238095241</v>
+        <v>457.26</v>
       </c>
       <c r="F178">
-        <v>1.401615678404754</v>
+        <v>1.4016</v>
       </c>
       <c r="G178">
         <v>234</v>
       </c>
       <c r="H178">
-        <v>3801.8149261194571</v>
+        <v>2667.1610071840901</v>
       </c>
       <c r="I178">
-        <v>277.63840545034395</v>
+        <v>277.63840545034401</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -6292,28 +6311,28 @@
         <v>186</v>
       </c>
       <c r="B179" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C179" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D179">
-        <v>2701.9711000000002</v>
+        <v>2701.97</v>
       </c>
       <c r="E179">
-        <v>516.39359999999999</v>
+        <v>516.39</v>
       </c>
       <c r="F179">
-        <v>1.1166667951456419</v>
+        <v>1.1167</v>
       </c>
       <c r="G179">
         <v>286</v>
       </c>
       <c r="H179">
-        <v>4083.1492306522969</v>
+        <v>2864.5309217157101</v>
       </c>
       <c r="I179">
-        <v>315.95514793645594</v>
+        <v>315.955147936456</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -6321,28 +6340,28 @@
         <v>187</v>
       </c>
       <c r="B180" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C180" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D180">
-        <v>2417.3450434782608</v>
+        <v>2417.35</v>
       </c>
       <c r="E180">
-        <v>470.48756521739131</v>
+        <v>470.49</v>
       </c>
       <c r="F180">
-        <v>1.182576708825783</v>
+        <v>1.1826000000000001</v>
       </c>
       <c r="G180">
         <v>285</v>
       </c>
       <c r="H180">
-        <v>4368.9696767979594</v>
+        <v>3065.0480862358099</v>
       </c>
       <c r="I180">
-        <v>294.25271930556806</v>
+        <v>294.25271930556801</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -6350,28 +6369,28 @@
         <v>188</v>
       </c>
       <c r="B181" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C181" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D181">
-        <v>2450.3712380952379</v>
+        <v>2450.37</v>
       </c>
       <c r="E181">
-        <v>485.96671428571432</v>
+        <v>485.97</v>
       </c>
       <c r="F181">
-        <v>1.230554148277315</v>
+        <v>1.2305999999999999</v>
       </c>
       <c r="G181">
         <v>284</v>
       </c>
       <c r="H181">
-        <v>4639.8457967594322</v>
+        <v>3255.08106758243</v>
       </c>
       <c r="I181">
-        <v>276.10193373238616</v>
+        <v>276.10193373238599</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -6379,28 +6398,28 @@
         <v>189</v>
       </c>
       <c r="B182" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C182" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D182">
-        <v>2707.6943999999999</v>
+        <v>2707.69</v>
       </c>
       <c r="E182">
-        <v>511.54829999999998</v>
+        <v>511.55</v>
       </c>
       <c r="F182">
-        <v>1.2817449668682459</v>
+        <v>1.2817000000000001</v>
       </c>
       <c r="G182">
         <v>286</v>
       </c>
       <c r="H182">
-        <v>4932.156081955276</v>
+        <v>3460.1511748401299</v>
       </c>
       <c r="I182">
-        <v>261.56755742935377</v>
+        <v>261.567557429354</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -6408,28 +6427,28 @@
         <v>190</v>
       </c>
       <c r="B183" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C183" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D183">
-        <v>2443.5201999999999</v>
+        <v>2443.52</v>
       </c>
       <c r="E183">
-        <v>455.45654999999999</v>
+        <v>455.46</v>
       </c>
       <c r="F183">
-        <v>1.1895530411219299</v>
+        <v>1.1896</v>
       </c>
       <c r="G183">
         <v>310</v>
       </c>
       <c r="H183">
-        <v>5173.8317299710834</v>
+        <v>3629.6985824072899</v>
       </c>
       <c r="I183">
-        <v>270.27386323004816</v>
+        <v>270.27386323004799</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,28 +6456,28 @@
         <v>191</v>
       </c>
       <c r="B184" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C184" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D184">
-        <v>2218.813714285714</v>
+        <v>2218.81</v>
       </c>
       <c r="E184">
-        <v>423.93852380952382</v>
+        <v>423.94</v>
       </c>
       <c r="F184">
-        <v>1.251266302623613</v>
+        <v>1.2513000000000001</v>
       </c>
       <c r="G184">
         <v>342</v>
       </c>
       <c r="H184">
-        <v>5437.6971481996088</v>
+        <v>3814.81321011006</v>
       </c>
       <c r="I184">
-        <v>283.70418717865158</v>
+        <v>283.70418717865198</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -6466,28 +6485,28 @@
         <v>192</v>
       </c>
       <c r="B185" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C185" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D185">
-        <v>1949.8928000000001</v>
+        <v>1949.89</v>
       </c>
       <c r="E185">
-        <v>408.27870000000001</v>
+        <v>408.28</v>
       </c>
       <c r="F185">
-        <v>1.2741214609455651</v>
+        <v>1.2741</v>
       </c>
       <c r="G185">
         <v>379</v>
       </c>
       <c r="H185">
-        <v>5763.9589770915854</v>
+        <v>4043.70200271667</v>
       </c>
       <c r="I185">
-        <v>296.60125493961425</v>
+        <v>296.60125493961402</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -6495,28 +6514,28 @@
         <v>193</v>
       </c>
       <c r="B186" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C186" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D186">
-        <v>1966.0121578947369</v>
+        <v>1966.01</v>
       </c>
       <c r="E186">
-        <v>408.05715789473692</v>
+        <v>408.06</v>
       </c>
       <c r="F186">
-        <v>1.171329943690566</v>
+        <v>1.1713</v>
       </c>
       <c r="G186">
         <v>373</v>
       </c>
       <c r="H186">
-        <v>6144.3802695796303</v>
+        <v>4310.5863348959701</v>
       </c>
       <c r="I186">
-        <v>273.83275849964627</v>
+        <v>273.83275849964599</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -6524,28 +6543,28 @@
         <v>194</v>
       </c>
       <c r="B187" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C187" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D187">
-        <v>2292.2567391304351</v>
+        <v>2292.2600000000002</v>
       </c>
       <c r="E187">
-        <v>445.52043478260867</v>
+        <v>445.52</v>
       </c>
       <c r="F187">
-        <v>1.1776221232719759</v>
+        <v>1.1776</v>
       </c>
       <c r="G187">
         <v>388</v>
       </c>
       <c r="H187">
-        <v>6617.4975503372634</v>
+        <v>4642.5014826829602</v>
       </c>
       <c r="I187">
-        <v>264.47985118493375</v>
+        <v>264.47985118493398</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -6553,28 +6572,28 @@
         <v>195</v>
       </c>
       <c r="B188" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C188" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D188">
-        <v>2501.5711500000002</v>
+        <v>2501.5700000000002</v>
       </c>
       <c r="E188">
-        <v>449.89415000000002</v>
+        <v>449.89</v>
       </c>
       <c r="F188">
-        <v>1.070521319337423</v>
+        <v>1.0705</v>
       </c>
       <c r="G188">
         <v>462</v>
       </c>
       <c r="H188">
-        <v>7173.3673445655922</v>
+        <v>5032.47160722833</v>
       </c>
       <c r="I188">
-        <v>290.51834378076472</v>
+        <v>290.51834378076501</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -6582,28 +6601,28 @@
         <v>196</v>
       </c>
       <c r="B189" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C189" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D189">
-        <v>2575.8785909090911</v>
+        <v>2575.88</v>
       </c>
       <c r="E189">
-        <v>444.09640909090899</v>
+        <v>444.1</v>
       </c>
       <c r="F189">
-        <v>1.132271190269593</v>
+        <v>1.1323000000000001</v>
       </c>
       <c r="G189">
         <v>485</v>
       </c>
       <c r="H189">
-        <v>7732.88999744171</v>
+        <v>5425.00439259214</v>
       </c>
       <c r="I189">
-        <v>282.91407997347756</v>
+        <v>282.91407997347801</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -6611,28 +6630,28 @@
         <v>197</v>
       </c>
       <c r="B190" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C190" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D190">
-        <v>2299.0884285714292</v>
+        <v>2299.09</v>
       </c>
       <c r="E190">
-        <v>415.18742857142848</v>
+        <v>415.19</v>
       </c>
       <c r="F190">
-        <v>1.1196837058934961</v>
+        <v>1.1196999999999999</v>
       </c>
       <c r="G190">
         <v>489</v>
       </c>
       <c r="H190">
-        <v>8196.8633972882126</v>
+        <v>5750.5046561476602</v>
       </c>
       <c r="I190">
-        <v>269.10131318231959</v>
+        <v>269.10131318231998</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -6640,16 +6659,16 @@
         <v>198</v>
       </c>
       <c r="B191" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C191" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D191">
-        <v>2013.8958</v>
+        <v>2013.9</v>
       </c>
       <c r="E191">
-        <v>388.73415</v>
+        <v>388.73</v>
       </c>
       <c r="F191">
         <v>1.1990000000000001</v>
@@ -6658,10 +6677,10 @@
         <v>545</v>
       </c>
       <c r="H191">
-        <v>8713.2657913173698</v>
+        <v>6112.78644948497</v>
       </c>
       <c r="I191">
-        <v>282.14359499653563</v>
+        <v>282.14359499653602</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -6669,16 +6688,16 @@
         <v>199</v>
       </c>
       <c r="B192" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C192" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D192">
-        <v>2053.344130434783</v>
+        <v>2053.34</v>
       </c>
       <c r="E192">
-        <v>386.17352173913042</v>
+        <v>386.17</v>
       </c>
       <c r="F192">
         <v>1.266</v>
@@ -6687,10 +6706,10 @@
         <v>725</v>
       </c>
       <c r="H192">
-        <v>9793.7107494407246</v>
+        <v>6870.7719692211003</v>
       </c>
       <c r="I192">
-        <v>333.92227361730437</v>
+        <v>333.92227361730397</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -6698,28 +6717,28 @@
         <v>200</v>
       </c>
       <c r="B193" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C193" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D193">
-        <v>2247.5088000000001</v>
+        <v>2247.5100000000002</v>
       </c>
       <c r="E193">
-        <v>391.02609999999999</v>
+        <v>391.03</v>
       </c>
       <c r="F193">
-        <v>1.0322588901684751</v>
+        <v>1.0323</v>
       </c>
       <c r="G193">
         <v>790</v>
       </c>
       <c r="H193">
-        <v>11037.5120146197</v>
+        <v>7743.3600093121804</v>
       </c>
       <c r="I193">
-        <v>322.85726054238648</v>
+        <v>322.857260542387</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -6727,28 +6746,28 @@
         <v>201</v>
       </c>
       <c r="B194" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C194" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D194">
-        <v>2540.2779523809518</v>
+        <v>2540.2800000000002</v>
       </c>
       <c r="E194">
-        <v>413.92414285714278</v>
+        <v>413.92</v>
       </c>
       <c r="F194">
-        <v>1.2227600938424881</v>
+        <v>1.2228000000000001</v>
       </c>
       <c r="G194">
         <v>870</v>
       </c>
       <c r="H194">
-        <v>11953.62551183313</v>
+        <v>8386.0588900850908</v>
       </c>
       <c r="I194">
-        <v>328.30255463828354</v>
+        <v>328.30255463828399</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -6756,28 +6775,28 @@
         <v>202</v>
       </c>
       <c r="B195" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C195" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D195">
-        <v>2327.4322857142861</v>
+        <v>2327.4299999999998</v>
       </c>
       <c r="E195">
         <v>402.07</v>
       </c>
       <c r="F195">
-        <v>1.4139523799488121</v>
+        <v>1.4139999999999999</v>
       </c>
       <c r="G195">
         <v>855</v>
       </c>
       <c r="H195">
-        <v>13483.68957734777</v>
+        <v>9459.4744280159903</v>
       </c>
       <c r="I195">
-        <v>286.03028879894475</v>
+        <v>286.03028879894498</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -6785,28 +6804,28 @@
         <v>203</v>
       </c>
       <c r="B196" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C196" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D196">
-        <v>1888.6986999999999</v>
+        <v>1888.7</v>
       </c>
       <c r="E196">
-        <v>373.16160000000002</v>
+        <v>373.16</v>
       </c>
       <c r="F196">
-        <v>2.8582238318659909</v>
+        <v>2.8582000000000001</v>
       </c>
       <c r="G196">
         <v>975</v>
       </c>
       <c r="H196">
-        <v>16922.030419571449</v>
+        <v>11871.640407160099</v>
       </c>
       <c r="I196">
-        <v>259.90031134313847</v>
+        <v>259.90031134313801</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -6814,28 +6833,28 @@
         <v>204</v>
       </c>
       <c r="B197" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C197" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D197">
-        <v>1948.955809523809</v>
+        <v>1948.96</v>
       </c>
       <c r="E197">
-        <v>377.70642857142849</v>
+        <v>377.71</v>
       </c>
       <c r="F197">
-        <v>2.609779887415379</v>
+        <v>2.6097999999999999</v>
       </c>
       <c r="G197">
         <v>1145</v>
       </c>
       <c r="H197">
-        <v>20407.96868600318</v>
+        <v>14317.198331035001</v>
       </c>
       <c r="I197">
-        <v>253.08147849461542</v>
+        <v>253.081478494615</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -6843,28 +6862,28 @@
         <v>205</v>
       </c>
       <c r="B198" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C198" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D198">
-        <v>1848.6364000000001</v>
+        <v>1848.64</v>
       </c>
       <c r="E198">
-        <v>361.70895000000002</v>
+        <v>361.71</v>
       </c>
       <c r="F198">
-        <v>2.5723347261684442</v>
+        <v>2.5722999999999998</v>
       </c>
       <c r="G198">
         <v>1000</v>
       </c>
       <c r="H198">
-        <v>23101.8205525556</v>
+        <v>16207.0685107317</v>
       </c>
       <c r="I198">
-        <v>195.25782592514341</v>
+        <v>195.25782592514301</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -6872,28 +6891,28 @@
         <v>206</v>
       </c>
       <c r="B199" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C199" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D199">
-        <v>1557.1141500000001</v>
+        <v>1557.11</v>
       </c>
       <c r="E199">
-        <v>336.68529999999998</v>
+        <v>336.69</v>
       </c>
       <c r="F199">
-        <v>2.5606388734993648</v>
+        <v>2.5606</v>
       </c>
       <c r="G199">
         <v>980</v>
       </c>
       <c r="H199">
-        <v>25643.02081333672</v>
+        <v>17989.846046912098</v>
       </c>
       <c r="I199">
-        <v>172.38979225823471</v>
+        <v>172.38979225823499</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -6901,28 +6920,28 @@
         <v>207</v>
       </c>
       <c r="B200" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C200" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D200">
-        <v>1282.941954545455</v>
+        <v>1282.94</v>
       </c>
       <c r="E200">
-        <v>322.84763636363641</v>
+        <v>322.85000000000002</v>
       </c>
       <c r="F200">
-        <v>2.4489384051170591</v>
+        <v>2.4489000000000001</v>
       </c>
       <c r="G200">
         <v>1010</v>
       </c>
       <c r="H200">
-        <v>27899.606644910349</v>
+        <v>19572.952499040399</v>
       </c>
       <c r="I200">
-        <v>163.2969033058383</v>
+        <v>163.29690330583799</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -6930,16 +6949,16 @@
         <v>208</v>
       </c>
       <c r="B201" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C201" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D201">
-        <v>1289.092272727273</v>
+        <v>1289.0899999999999</v>
       </c>
       <c r="E201">
-        <v>411.27499999999998</v>
+        <v>411.27</v>
       </c>
       <c r="F201">
         <v>2.5139999999999998</v>
@@ -6948,10 +6967,10 @@
         <v>1195</v>
       </c>
       <c r="H201">
-        <v>29071.390123996589</v>
+        <v>20395.016504000101</v>
       </c>
       <c r="I201">
-        <v>185.42007891381462</v>
+        <v>185.42007891381499</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -6959,16 +6978,16 @@
         <v>209</v>
       </c>
       <c r="B202" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C202" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D202">
-        <v>1456.131052631579</v>
+        <v>1456.13</v>
       </c>
       <c r="E202">
-        <v>457.9487894736842</v>
+        <v>457.95</v>
       </c>
       <c r="F202">
         <v>2.4620000000000002</v>
@@ -6977,10 +6996,10 @@
         <v>1335</v>
       </c>
       <c r="H202">
-        <v>30408.674069700432</v>
+        <v>21333.1872631841</v>
       </c>
       <c r="I202">
-        <v>198.03339708148394</v>
+        <v>198.033397081484</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -6988,28 +7007,28 @@
         <v>210</v>
       </c>
       <c r="B203" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C203" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D203">
-        <v>1535.5408636363641</v>
+        <v>1535.54</v>
       </c>
       <c r="E203">
-        <v>469.05118181818182</v>
+        <v>469.05</v>
       </c>
       <c r="F203">
-        <v>2.371791659866759</v>
+        <v>2.3717999999999999</v>
       </c>
       <c r="G203">
         <v>1340</v>
       </c>
       <c r="H203">
-        <v>31625.02103248845</v>
+        <v>22186.514753711501</v>
       </c>
       <c r="I203">
-        <v>191.12989922874425</v>
+        <v>191.12989922874399</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -7017,28 +7036,28 @@
         <v>211</v>
       </c>
       <c r="B204" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C204" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D204">
-        <v>1529.6168636363641</v>
+        <v>1529.62</v>
       </c>
       <c r="E204">
-        <v>477.61363636363637</v>
+        <v>477.61</v>
       </c>
       <c r="F204">
-        <v>2.5372328150020458</v>
+        <v>2.5371999999999999</v>
       </c>
       <c r="G204">
         <v>1275</v>
       </c>
       <c r="H204">
-        <v>32953.271915852973</v>
+        <v>23118.3483733674</v>
       </c>
       <c r="I204">
-        <v>174.52847675011378</v>
+        <v>174.52847675011401</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -7046,28 +7065,28 @@
         <v>212</v>
       </c>
       <c r="B205" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C205" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D205">
-        <v>1377.2731000000001</v>
+        <v>1377.27</v>
       </c>
       <c r="E205">
-        <v>462.54829999999998</v>
+        <v>462.55</v>
       </c>
       <c r="F205">
-        <v>2.160839974385047</v>
+        <v>2.1608000000000001</v>
       </c>
       <c r="G205">
         <v>1205</v>
       </c>
       <c r="H205">
-        <v>34106.636432907821</v>
+        <v>23927.490566435201</v>
       </c>
       <c r="I205">
-        <v>159.36861948196429</v>
+        <v>159.368619481964</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -7075,16 +7094,16 @@
         <v>213</v>
       </c>
       <c r="B206" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C206" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D206">
-        <v>1099.4633181818181</v>
+        <v>1099.46</v>
       </c>
       <c r="E206">
-        <v>432.21327272727268</v>
+        <v>432.21</v>
       </c>
       <c r="F206">
         <v>2.4249999999999998</v>
@@ -7093,10 +7112,10 @@
         <v>1150</v>
       </c>
       <c r="H206">
-        <v>35027.515616596327</v>
+        <v>24573.532811729001</v>
       </c>
       <c r="I206">
-        <v>148.09594266364908</v>
+        <v>148.095942663649</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -7104,16 +7123,16 @@
         <v>214</v>
       </c>
       <c r="B207" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C207" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D207">
-        <v>805.26215789473679</v>
+        <v>805.26</v>
       </c>
       <c r="E207">
-        <v>426.47705263157889</v>
+        <v>426.48</v>
       </c>
       <c r="F207">
         <v>2.6640000000000001</v>
@@ -7122,10 +7141,10 @@
         <v>1090</v>
       </c>
       <c r="H207">
-        <v>35868.175991394652</v>
+        <v>25163.297599210498</v>
       </c>
       <c r="I207">
-        <v>137.07929475490616</v>
+        <v>137.07929475490599</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -7133,16 +7152,16 @@
         <v>215</v>
       </c>
       <c r="B208" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C208" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D208">
-        <v>693.47952380952381</v>
+        <v>693.48</v>
       </c>
       <c r="E208">
-        <v>423.544380952381</v>
+        <v>423.54</v>
       </c>
       <c r="F208">
         <v>2.6549999999999998</v>
@@ -7151,10 +7170,10 @@
         <v>1195</v>
       </c>
       <c r="H208">
-        <v>36836.616743162303</v>
+        <v>25842.7066343892</v>
       </c>
       <c r="I208">
-        <v>146.33318495315729</v>
+        <v>146.333184953157</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
@@ -7162,16 +7181,16 @@
         <v>216</v>
       </c>
       <c r="B209" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C209" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D209">
-        <v>606.23957142857137</v>
+        <v>606.24</v>
       </c>
       <c r="E209">
-        <v>418.07733333333329</v>
+        <v>418.08</v>
       </c>
       <c r="F209">
         <v>2.605</v>
@@ -7180,10 +7199,10 @@
         <v>1200</v>
       </c>
       <c r="H209">
-        <v>37647.022311511857</v>
+        <v>26411.246180345701</v>
       </c>
       <c r="I209">
-        <v>143.78224823243352</v>
+        <v>143.782248232434</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -7191,16 +7210,16 @@
         <v>217</v>
       </c>
       <c r="B210" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C210" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D210">
-        <v>699.34768421052627</v>
+        <v>699.35</v>
       </c>
       <c r="E210">
-        <v>416.03815789473691</v>
+        <v>416.04</v>
       </c>
       <c r="F210">
         <v>2.5579999999999998</v>
@@ -7209,10 +7228,10 @@
         <v>1210</v>
       </c>
       <c r="H210">
-        <v>38550.550846988153</v>
+        <v>27045.116088674</v>
       </c>
       <c r="I210">
-        <v>141.58245472106489</v>
+        <v>141.58245472106501</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -7220,16 +7239,16 @@
         <v>218</v>
       </c>
       <c r="B211" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C211" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D211">
-        <v>750.89114285714288</v>
+        <v>750.89</v>
       </c>
       <c r="E211">
-        <v>430.17119047619042</v>
+        <v>430.17</v>
       </c>
       <c r="F211">
         <v>2.42</v>
@@ -7238,10 +7257,10 @@
         <v>1280</v>
       </c>
       <c r="H211">
-        <v>39976.921228326697</v>
+        <v>28045.785383955001</v>
       </c>
       <c r="I211">
-        <v>144.42929145816612</v>
+        <v>144.42929145816601</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7249,16 +7268,16 @@
         <v>219</v>
       </c>
       <c r="B212" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C212" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D212">
-        <v>790.81061904761907</v>
+        <v>790.81</v>
       </c>
       <c r="E212">
-        <v>460.40333333333331</v>
+        <v>460.4</v>
       </c>
       <c r="F212">
         <v>2.331</v>
@@ -7267,10 +7286,10 @@
         <v>1180</v>
       </c>
       <c r="H212">
-        <v>41096.275022719863</v>
+        <v>28831.067374705701</v>
       </c>
       <c r="I212">
-        <v>129.51921504182579</v>
+        <v>129.51921504182599</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -7278,16 +7297,16 @@
         <v>220</v>
       </c>
       <c r="B213" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C213" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D213">
-        <v>675.47523809523807</v>
+        <v>675.48</v>
       </c>
       <c r="E213">
-        <v>421.41947619047608</v>
+        <v>421.42</v>
       </c>
       <c r="F213">
         <v>2.448</v>
@@ -7296,10 +7315,10 @@
         <v>1160</v>
       </c>
       <c r="H213">
-        <v>41712.719148060649</v>
+        <v>29263.5333853263</v>
       </c>
       <c r="I213">
-        <v>125.44233902356008</v>
+        <v>125.44233902356</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -7307,16 +7326,16 @@
         <v>221</v>
       </c>
       <c r="B214" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C214" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D214">
-        <v>690.11525000000006</v>
+        <v>690.12</v>
       </c>
       <c r="E214">
-        <v>406.98079999999999</v>
+        <v>406.98</v>
       </c>
       <c r="F214">
         <v>2.3359999999999999</v>
@@ -7325,10 +7344,10 @@
         <v>1190</v>
       </c>
       <c r="H214">
-        <v>42380.122654429622</v>
+        <v>29731.7499194915</v>
       </c>
       <c r="I214">
-        <v>126.6599778017551</v>
+        <v>126.65997780175501</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -7336,16 +7355,16 @@
         <v>222</v>
       </c>
       <c r="B215" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C215" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D215">
-        <v>729.07440909090917</v>
+        <v>729.07</v>
       </c>
       <c r="E215">
-        <v>387.57290909090898</v>
+        <v>387.57</v>
       </c>
       <c r="F215">
         <v>2.4510000000000001</v>
@@ -7354,10 +7373,10 @@
         <v>1300</v>
       </c>
       <c r="H215">
-        <v>43185.344984863783</v>
+        <v>30296.653167961798</v>
       </c>
       <c r="I215">
-        <v>135.78806965329463</v>
+        <v>135.788069653295</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -7365,16 +7384,16 @@
         <v>223</v>
       </c>
       <c r="B216" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C216" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D216">
-        <v>758.01809523809527</v>
+        <v>758.02</v>
       </c>
       <c r="E216">
-        <v>370.00742857142859</v>
+        <v>370.01</v>
       </c>
       <c r="F216">
         <v>2.1179999999999999</v>
@@ -7383,10 +7402,10 @@
         <v>1300</v>
       </c>
       <c r="H216">
-        <v>44005.866539576193</v>
+        <v>30872.289578153101</v>
       </c>
       <c r="I216">
-        <v>133.25620181873862</v>
+        <v>133.25620181873899</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -7394,28 +7413,28 @@
         <v>224</v>
       </c>
       <c r="B217" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C217" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D217">
-        <v>1091.348</v>
+        <v>1091.3499999999999</v>
       </c>
       <c r="E217">
-        <v>360.21300000000002</v>
+        <v>360.21</v>
       </c>
       <c r="F217">
-        <v>1.9439660000000001</v>
+        <v>1.944</v>
       </c>
       <c r="G217">
         <v>1425</v>
       </c>
       <c r="H217">
-        <v>44929.989736907279</v>
+        <v>31520.607659294299</v>
       </c>
       <c r="I217">
-        <v>143.06493452249117</v>
+        <v>143.064934522491</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -7423,28 +7442,28 @@
         <v>225</v>
       </c>
       <c r="B218" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C218" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D218">
-        <v>975.09995454545458</v>
+        <v>975.1</v>
       </c>
       <c r="E218">
-        <v>347.80927272727268</v>
+        <v>347.81</v>
       </c>
       <c r="F218">
-        <v>2.1011280000000001</v>
+        <v>2.1011000000000002</v>
       </c>
       <c r="G218">
         <v>1425</v>
       </c>
       <c r="H218">
-        <v>45963.379500856143</v>
+        <v>32245.5816354581</v>
       </c>
       <c r="I218">
-        <v>139.84842084309992</v>
+        <v>139.8484208431</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -7452,28 +7471,28 @@
         <v>226</v>
       </c>
       <c r="B219" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D219">
-        <v>631.32333333333327</v>
+        <v>631.32000000000005</v>
       </c>
       <c r="E219">
-        <v>323.56927777777781</v>
+        <v>323.57</v>
       </c>
       <c r="F219">
-        <v>2.4683519999999999</v>
+        <v>2.4683999999999999</v>
       </c>
       <c r="G219">
         <v>1415</v>
       </c>
       <c r="H219">
-        <v>47112.463988377538</v>
+        <v>33051.721176344501</v>
       </c>
       <c r="I219">
-        <v>135.48002772305443</v>
+        <v>135.48002772305401</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -7481,28 +7500,28 @@
         <v>227</v>
       </c>
       <c r="B220" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C220" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D220">
-        <v>598.94163636363635</v>
+        <v>598.94000000000005</v>
       </c>
       <c r="E220">
-        <v>311.79854545454549</v>
+        <v>311.8</v>
       </c>
       <c r="F220">
-        <v>2.4647260000000002</v>
+        <v>2.4647000000000001</v>
       </c>
       <c r="G220">
         <v>1510</v>
       </c>
       <c r="H220">
-        <v>48431.612980052108</v>
+        <v>33977.169369282201</v>
       </c>
       <c r="I220">
-        <v>140.63799608269665</v>
+        <v>140.63799608269699</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -7510,28 +7529,28 @@
         <v>228</v>
       </c>
       <c r="B221" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C221" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D221">
-        <v>546.72345000000007</v>
+        <v>546.72</v>
       </c>
       <c r="E221">
-        <v>294.90255000000002</v>
+        <v>294.89999999999998</v>
       </c>
       <c r="F221">
-        <v>2.3968782200000001</v>
+        <v>2.3969</v>
       </c>
       <c r="G221">
         <v>1450</v>
       </c>
       <c r="H221">
-        <v>49836.129756473623</v>
+        <v>34962.507280991398</v>
       </c>
       <c r="I221">
-        <v>131.24366505120392</v>
+        <v>131.243665051204</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -7539,28 +7558,28 @@
         <v>229</v>
       </c>
       <c r="B222" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C222" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D222">
-        <v>519.14789473684209</v>
+        <v>519.15</v>
       </c>
       <c r="E222">
-        <v>287.7625263157895</v>
+        <v>287.76</v>
       </c>
       <c r="F222">
-        <v>2.3834059999999999</v>
+        <v>2.3834</v>
       </c>
       <c r="G222">
         <v>1405</v>
       </c>
       <c r="H222">
-        <v>51281.377519411362</v>
+        <v>35976.419992140101</v>
       </c>
       <c r="I222">
-        <v>123.58657511272513</v>
+        <v>123.586575112725</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -7568,28 +7587,28 @@
         <v>230</v>
       </c>
       <c r="B223" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C223" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D223">
-        <v>585.46013636363637</v>
+        <v>585.46</v>
       </c>
       <c r="E223">
-        <v>298.50086363636359</v>
+        <v>298.5</v>
       </c>
       <c r="F223">
-        <v>2.3008899999999999</v>
+        <v>2.3008999999999999</v>
       </c>
       <c r="G223">
         <v>1390</v>
       </c>
       <c r="H223">
-        <v>53024.944355071333</v>
+        <v>37199.618271872903</v>
       </c>
       <c r="I223">
-        <v>118.24675578838213</v>
+        <v>118.246755788382</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -7597,28 +7616,28 @@
         <v>231</v>
       </c>
       <c r="B224" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C224" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D224">
-        <v>561.18272727272733</v>
+        <v>561.17999999999995</v>
       </c>
       <c r="E224">
-        <v>276.76954545454549</v>
+        <v>276.77</v>
       </c>
       <c r="F224">
-        <v>2.023031</v>
+        <v>2.0230000000000001</v>
       </c>
       <c r="G224">
         <v>1395</v>
       </c>
       <c r="H224">
-        <v>54403.592908303202</v>
+        <v>38166.808346941601</v>
       </c>
       <c r="I224">
-        <v>115.66481854852472</v>
+        <v>115.66481854852501</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -7626,16 +7645,16 @@
         <v>232</v>
       </c>
       <c r="B225" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C225" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D225">
-        <v>521.26385000000005</v>
+        <v>521.26</v>
       </c>
       <c r="E225">
-        <v>258.38664999999997</v>
+        <v>258.39</v>
       </c>
       <c r="F225">
         <v>1.99</v>
@@ -7644,10 +7663,10 @@
         <v>1410</v>
       </c>
       <c r="H225">
-        <v>55546.068359377547</v>
+        <v>38968.311322227302</v>
       </c>
       <c r="I225">
-        <v>114.50394346214784</v>
+        <v>114.503943462148</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -7655,16 +7674,16 @@
         <v>233</v>
       </c>
       <c r="B226" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C226" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D226">
-        <v>455.25376190476192</v>
+        <v>455.25</v>
       </c>
       <c r="E226">
-        <v>251.85400000000001</v>
+        <v>251.85</v>
       </c>
       <c r="F226">
         <v>2.0699999999999998</v>
@@ -7673,10 +7692,10 @@
         <v>1495</v>
       </c>
       <c r="H226">
-        <v>56601.443658205717</v>
+        <v>39708.7092373497</v>
       </c>
       <c r="I226">
-        <v>119.14294745642096</v>
+        <v>119.142947456421</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -7684,93 +7703,112 @@
         <v>234</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C227" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D227">
-        <v>419.35550000000001</v>
+        <v>419.36</v>
       </c>
       <c r="E227">
-        <v>252.65509090909089</v>
+        <v>252.66</v>
       </c>
       <c r="F227">
-        <v>1.9355526222675601</v>
+        <v>1.9356</v>
       </c>
       <c r="G227">
         <v>1540</v>
       </c>
       <c r="H227">
-        <v>57790.073975028041</v>
+        <v>40542.592131334</v>
       </c>
       <c r="I227">
-        <v>120.20488738687452</v>
+        <v>120.204887386875</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B228" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C228" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D228">
-        <v>483</v>
+        <v>482.54239999999999</v>
       </c>
       <c r="E228">
-        <v>253.584</v>
+        <v>255.2627</v>
       </c>
       <c r="F228">
-        <v>2.06</v>
+        <v>2.0587</v>
       </c>
       <c r="G228">
-        <v>1590</v>
+        <v>1587.2538</v>
       </c>
       <c r="H228">
-        <v>58772.505232603515</v>
+        <v>41231.816197566703</v>
       </c>
       <c r="I228">
-        <v>122.03308109229494</v>
+        <v>121.82230923865001</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B229" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C229" t="s">
+        <v>244</v>
+      </c>
+      <c r="D229" s="1">
+        <v>534</v>
+      </c>
+      <c r="E229">
+        <v>250.7176</v>
+      </c>
+      <c r="F229">
+        <v>1.9369899463922899</v>
+      </c>
+      <c r="G229">
+        <v>1597</v>
+      </c>
+      <c r="H229">
+        <v>42015.220705320426</v>
+      </c>
+      <c r="I229">
+        <v>120.28492016738267</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>245</v>
+      </c>
+      <c r="B230" t="s">
         <v>242</v>
       </c>
-      <c r="D229">
-        <v>642</v>
-      </c>
-      <c r="E229">
-        <v>250</v>
-      </c>
-      <c r="F229">
-        <v>1.94</v>
-      </c>
-      <c r="G229">
-        <v>1625</v>
-      </c>
-      <c r="H229">
-        <v>59947.955337255589</v>
-      </c>
-      <c r="I229">
-        <v>122.65009383428335</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H231" s="1"/>
+      <c r="C230" t="s">
+        <v>244</v>
+      </c>
+      <c r="D230" s="2">
+        <v>635</v>
+      </c>
+      <c r="E230">
+        <v>275.072</v>
+      </c>
+      <c r="F230">
+        <v>1.95</v>
+      </c>
+      <c r="G230">
+        <v>1640</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/serie_modelo.xlsx
+++ b/data/serie_modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\excel_simulador_electoral\SEPT26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F346819FD96AA6D9731F737A19CA3255452DE7CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB2E6FD-A757-4CF9-AF7D-C8E0942D7369}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_F346819FD96AA6D9731F737A19CA3255452DE7CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DA60988-5321-4535-8AB7-33FCF8708A5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7807,6 +7807,12 @@
       <c r="G230">
         <v>1640</v>
       </c>
+      <c r="H230">
+        <v>42813.50989872151</v>
+      </c>
+      <c r="I230">
+        <v>121.22046125156622</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
